--- a/research/traditional_assets/database/data/south_korea/south_korea_tobacco.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_tobacco.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07360317640685958</v>
+        <v>0.07345291846584241</v>
       </c>
       <c r="C2">
-        <v>7820.3</v>
+        <v>7776.518466433328</v>
       </c>
       <c r="D2">
-        <v>6334.8</v>
+        <v>6369.221466433329</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>78.203</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>78.203</v>
       </c>
       <c r="G2">
         <v>1485.5</v>
@@ -1457,28 +1457,28 @@
         <v>1017.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.9336109</v>
       </c>
       <c r="N2">
-        <v>1017.3</v>
+        <v>1013.3663891</v>
       </c>
       <c r="O2">
-        <v>254.325</v>
+        <v>253.341597275</v>
       </c>
       <c r="P2">
-        <v>762.975</v>
+        <v>760.0247918250001</v>
       </c>
       <c r="Q2">
-        <v>826.575</v>
+        <v>823.6247918250001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07360317640685958</v>
+        <v>0.07381380653115396</v>
       </c>
       <c r="T2">
-        <v>0.5572774141861078</v>
+        <v>0.5614992127784267</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>258.6173431642667</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07345291846584241</v>
+        <v>0.07330266052482529</v>
       </c>
       <c r="C3">
-        <v>7776.518466433328</v>
+        <v>7733.113049109538</v>
       </c>
       <c r="D3">
-        <v>6369.221466433329</v>
+        <v>6404.019049109538</v>
       </c>
       <c r="E3">
-        <v>78.203</v>
+        <v>156.406</v>
       </c>
       <c r="F3">
-        <v>78.203</v>
+        <v>156.406</v>
       </c>
       <c r="G3">
         <v>1485.5</v>
@@ -1539,28 +1539,28 @@
         <v>1017.3</v>
       </c>
       <c r="M3">
-        <v>3.9336109</v>
+        <v>7.8672218</v>
       </c>
       <c r="N3">
-        <v>1013.3663891</v>
+        <v>1009.4327782</v>
       </c>
       <c r="O3">
-        <v>253.341597275</v>
+        <v>252.35819455</v>
       </c>
       <c r="P3">
-        <v>760.0247918250001</v>
+        <v>757.07458365</v>
       </c>
       <c r="Q3">
-        <v>823.6247918250001</v>
+        <v>820.67458365</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07381380653115396</v>
+        <v>0.07402873522941356</v>
       </c>
       <c r="T3">
-        <v>0.5614992127784267</v>
+        <v>0.5658071705256911</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>258.6173431642667</v>
+        <v>129.3086715821333</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07330266052482529</v>
+        <v>0.07315240258380813</v>
       </c>
       <c r="C4">
-        <v>7733.113049109538</v>
+        <v>7690.089946509976</v>
       </c>
       <c r="D4">
-        <v>6404.019049109538</v>
+        <v>6439.198946509976</v>
       </c>
       <c r="E4">
-        <v>156.406</v>
+        <v>234.609</v>
       </c>
       <c r="F4">
-        <v>156.406</v>
+        <v>234.609</v>
       </c>
       <c r="G4">
         <v>1485.5</v>
@@ -1621,28 +1621,28 @@
         <v>1017.3</v>
       </c>
       <c r="M4">
-        <v>7.8672218</v>
+        <v>11.8008327</v>
       </c>
       <c r="N4">
-        <v>1009.4327782</v>
+        <v>1005.4991673</v>
       </c>
       <c r="O4">
-        <v>252.35819455</v>
+        <v>251.374791825</v>
       </c>
       <c r="P4">
-        <v>757.07458365</v>
+        <v>754.1243754750001</v>
       </c>
       <c r="Q4">
-        <v>820.67458365</v>
+        <v>817.7243754750001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07402873522941356</v>
+        <v>0.07424809544722488</v>
       </c>
       <c r="T4">
-        <v>0.5658071705256911</v>
+        <v>0.5702039521440329</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>129.3086715821333</v>
+        <v>86.20578105475558</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07315240258380813</v>
+        <v>0.07300214464279098</v>
       </c>
       <c r="C5">
-        <v>7690.089946509976</v>
+        <v>7647.455494071494</v>
       </c>
       <c r="D5">
-        <v>6439.198946509976</v>
+        <v>6474.767494071494</v>
       </c>
       <c r="E5">
-        <v>234.609</v>
+        <v>312.812</v>
       </c>
       <c r="F5">
-        <v>234.609</v>
+        <v>312.812</v>
       </c>
       <c r="G5">
         <v>1485.5</v>
@@ -1703,28 +1703,28 @@
         <v>1017.3</v>
       </c>
       <c r="M5">
-        <v>11.8008327</v>
+        <v>15.7344436</v>
       </c>
       <c r="N5">
-        <v>1005.4991673</v>
+        <v>1001.5655564</v>
       </c>
       <c r="O5">
-        <v>251.374791825</v>
+        <v>250.3913891</v>
       </c>
       <c r="P5">
-        <v>754.1243754750001</v>
+        <v>751.1741673000001</v>
       </c>
       <c r="Q5">
-        <v>817.7243754750001</v>
+        <v>814.7741673000002</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07424809544722488</v>
+        <v>0.07447202566957395</v>
       </c>
       <c r="T5">
-        <v>0.5702039521440329</v>
+        <v>0.5746923333794236</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>86.20578105475558</v>
+        <v>64.65433579106667</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07300214464279098</v>
+        <v>0.07285188670177384</v>
       </c>
       <c r="C6">
-        <v>7647.455494071494</v>
+        <v>7605.216167990036</v>
       </c>
       <c r="D6">
-        <v>6474.767494071494</v>
+        <v>6510.731167990036</v>
       </c>
       <c r="E6">
-        <v>312.812</v>
+        <v>391.015</v>
       </c>
       <c r="F6">
-        <v>312.812</v>
+        <v>391.015</v>
       </c>
       <c r="G6">
         <v>1485.5</v>
@@ -1785,28 +1785,28 @@
         <v>1017.3</v>
       </c>
       <c r="M6">
-        <v>15.7344436</v>
+        <v>19.6680545</v>
       </c>
       <c r="N6">
-        <v>1001.5655564</v>
+        <v>997.6319455</v>
       </c>
       <c r="O6">
-        <v>250.3913891</v>
+        <v>249.407986375</v>
       </c>
       <c r="P6">
-        <v>751.1741673000001</v>
+        <v>748.223959125</v>
       </c>
       <c r="Q6">
-        <v>814.7741673000002</v>
+        <v>811.823959125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07447202566957395</v>
+        <v>0.07470067021239352</v>
       </c>
       <c r="T6">
-        <v>0.5746923333794236</v>
+        <v>0.5792752068513489</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>64.65433579106667</v>
+        <v>51.72346863285334</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07285188670177384</v>
+        <v>0.07270162876075668</v>
       </c>
       <c r="C7">
-        <v>7605.216167990036</v>
+        <v>7563.378589151652</v>
       </c>
       <c r="D7">
-        <v>6510.731167990036</v>
+        <v>6547.096589151652</v>
       </c>
       <c r="E7">
-        <v>391.015</v>
+        <v>469.2180000000001</v>
       </c>
       <c r="F7">
-        <v>391.015</v>
+        <v>469.2180000000001</v>
       </c>
       <c r="G7">
         <v>1485.5</v>
@@ -1867,28 +1867,28 @@
         <v>1017.3</v>
       </c>
       <c r="M7">
-        <v>19.6680545</v>
+        <v>23.6016654</v>
       </c>
       <c r="N7">
-        <v>997.6319455</v>
+        <v>993.6983346000001</v>
       </c>
       <c r="O7">
-        <v>249.407986375</v>
+        <v>248.42458365</v>
       </c>
       <c r="P7">
-        <v>748.223959125</v>
+        <v>745.27375095</v>
       </c>
       <c r="Q7">
-        <v>811.823959125</v>
+        <v>808.87375095</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07470067021239352</v>
+        <v>0.07493417953271989</v>
       </c>
       <c r="T7">
-        <v>0.5792752068513489</v>
+        <v>0.5839555882694852</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>51.72346863285334</v>
+        <v>43.10289052737778</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07270162876075668</v>
+        <v>0.07255137081973953</v>
       </c>
       <c r="C8">
-        <v>7563.378589151652</v>
+        <v>7521.949527195996</v>
       </c>
       <c r="D8">
-        <v>6547.096589151652</v>
+        <v>6583.870527195996</v>
       </c>
       <c r="E8">
-        <v>469.218</v>
+        <v>547.4209999999999</v>
       </c>
       <c r="F8">
-        <v>469.218</v>
+        <v>547.4209999999999</v>
       </c>
       <c r="G8">
         <v>1485.5</v>
@@ -1949,28 +1949,28 @@
         <v>1017.3</v>
       </c>
       <c r="M8">
-        <v>23.6016654</v>
+        <v>27.5352763</v>
       </c>
       <c r="N8">
-        <v>993.6983346000001</v>
+        <v>989.7647237000001</v>
       </c>
       <c r="O8">
-        <v>248.42458365</v>
+        <v>247.441180925</v>
       </c>
       <c r="P8">
-        <v>745.27375095</v>
+        <v>742.3235427750001</v>
       </c>
       <c r="Q8">
-        <v>808.87375095</v>
+        <v>805.9235427750001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07493417953271989</v>
+        <v>0.07517271055885971</v>
       </c>
       <c r="T8">
-        <v>0.5839555882694852</v>
+        <v>0.5887366230514526</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>43.10289052737779</v>
+        <v>36.9453347377524</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07255137081973953</v>
+        <v>0.07240111287872239</v>
       </c>
       <c r="C9">
-        <v>7521.949527195996</v>
+        <v>7480.935904717535</v>
       </c>
       <c r="D9">
-        <v>6583.870527195996</v>
+        <v>6621.059904717535</v>
       </c>
       <c r="E9">
-        <v>547.421</v>
+        <v>625.624</v>
       </c>
       <c r="F9">
-        <v>547.421</v>
+        <v>625.624</v>
       </c>
       <c r="G9">
         <v>1485.5</v>
@@ -2031,28 +2031,28 @@
         <v>1017.3</v>
       </c>
       <c r="M9">
-        <v>27.5352763</v>
+        <v>31.4688872</v>
       </c>
       <c r="N9">
-        <v>989.7647237000001</v>
+        <v>985.8311128</v>
       </c>
       <c r="O9">
-        <v>247.441180925</v>
+        <v>246.4577782</v>
       </c>
       <c r="P9">
-        <v>742.3235427750001</v>
+        <v>739.3733346</v>
       </c>
       <c r="Q9">
-        <v>805.9235427750001</v>
+        <v>802.9733346</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07517271055885971</v>
+        <v>0.07541642704208956</v>
       </c>
       <c r="T9">
-        <v>0.5887366230514526</v>
+        <v>0.5936215933721584</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>36.94533473775239</v>
+        <v>32.32716789553334</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07240111287872239</v>
+        <v>0.07225085493770524</v>
       </c>
       <c r="C10">
-        <v>7480.935904717535</v>
+        <v>7440.344801609985</v>
       </c>
       <c r="D10">
-        <v>6621.059904717535</v>
+        <v>6658.671801609985</v>
       </c>
       <c r="E10">
-        <v>625.624</v>
+        <v>703.827</v>
       </c>
       <c r="F10">
-        <v>625.624</v>
+        <v>703.827</v>
       </c>
       <c r="G10">
         <v>1485.5</v>
@@ -2113,28 +2113,28 @@
         <v>1017.3</v>
       </c>
       <c r="M10">
-        <v>31.4688872</v>
+        <v>35.4024981</v>
       </c>
       <c r="N10">
-        <v>985.8311128</v>
+        <v>981.8975019000001</v>
       </c>
       <c r="O10">
-        <v>246.4577782</v>
+        <v>245.474375475</v>
       </c>
       <c r="P10">
-        <v>739.3733346</v>
+        <v>736.4231264250001</v>
       </c>
       <c r="Q10">
-        <v>802.9733346</v>
+        <v>800.0231264250001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07541642704208956</v>
+        <v>0.07566549993154421</v>
       </c>
       <c r="T10">
-        <v>0.5936215933721584</v>
+        <v>0.5986139256779344</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>32.32716789553334</v>
+        <v>28.73526035158519</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07225085493770524</v>
+        <v>0.0721005969966881</v>
       </c>
       <c r="C11">
-        <v>7440.344801609985</v>
+        <v>7400.183459559605</v>
       </c>
       <c r="D11">
-        <v>6658.671801609985</v>
+        <v>6696.713459559604</v>
       </c>
       <c r="E11">
-        <v>703.827</v>
+        <v>782.03</v>
       </c>
       <c r="F11">
-        <v>703.827</v>
+        <v>782.03</v>
       </c>
       <c r="G11">
         <v>1485.5</v>
@@ -2195,28 +2195,28 @@
         <v>1017.3</v>
       </c>
       <c r="M11">
-        <v>35.4024981</v>
+        <v>39.33610899999999</v>
       </c>
       <c r="N11">
-        <v>981.8975019000001</v>
+        <v>977.9638910000001</v>
       </c>
       <c r="O11">
-        <v>245.474375475</v>
+        <v>244.49097275</v>
       </c>
       <c r="P11">
-        <v>736.4231264250001</v>
+        <v>733.47291825</v>
       </c>
       <c r="Q11">
-        <v>800.0231264250001</v>
+        <v>797.07291825</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07566549993154421</v>
+        <v>0.07592010777409788</v>
       </c>
       <c r="T11">
-        <v>0.5986139256779344</v>
+        <v>0.6037171987016167</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>28.73526035158519</v>
+        <v>25.86173431642668</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0721005969966881</v>
+        <v>0.07195033905567094</v>
       </c>
       <c r="C12">
-        <v>7400.183459559605</v>
+        <v>7360.459286693476</v>
       </c>
       <c r="D12">
-        <v>6696.713459559604</v>
+        <v>6735.192286693476</v>
       </c>
       <c r="E12">
-        <v>782.0300000000001</v>
+        <v>860.2330000000001</v>
       </c>
       <c r="F12">
-        <v>782.0300000000001</v>
+        <v>860.2330000000001</v>
       </c>
       <c r="G12">
         <v>1485.5</v>
@@ -2277,28 +2277,28 @@
         <v>1017.3</v>
       </c>
       <c r="M12">
-        <v>39.336109</v>
+        <v>43.2697199</v>
       </c>
       <c r="N12">
-        <v>977.9638910000001</v>
+        <v>974.0302801</v>
       </c>
       <c r="O12">
-        <v>244.49097275</v>
+        <v>243.507570025</v>
       </c>
       <c r="P12">
-        <v>733.47291825</v>
+        <v>730.5227100750001</v>
       </c>
       <c r="Q12">
-        <v>797.07291825</v>
+        <v>794.1227100750001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07592010777409788</v>
+        <v>0.07618043714120332</v>
       </c>
       <c r="T12">
-        <v>0.6037171987016167</v>
+        <v>0.6089351520179661</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.86173431642667</v>
+        <v>23.51066756038788</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07195033905567094</v>
+        <v>0.07180008111465379</v>
       </c>
       <c r="C13">
-        <v>7360.459286693476</v>
+        <v>7321.179862388892</v>
       </c>
       <c r="D13">
-        <v>6735.192286693476</v>
+        <v>6774.115862388892</v>
       </c>
       <c r="E13">
-        <v>860.2330000000001</v>
+        <v>938.436</v>
       </c>
       <c r="F13">
-        <v>860.2330000000001</v>
+        <v>938.436</v>
       </c>
       <c r="G13">
         <v>1485.5</v>
@@ -2359,28 +2359,28 @@
         <v>1017.3</v>
       </c>
       <c r="M13">
-        <v>43.2697199</v>
+        <v>47.2033308</v>
       </c>
       <c r="N13">
-        <v>974.0302801</v>
+        <v>970.0966692000001</v>
       </c>
       <c r="O13">
-        <v>243.507570025</v>
+        <v>242.5241673</v>
       </c>
       <c r="P13">
-        <v>730.5227100750001</v>
+        <v>727.5725019</v>
       </c>
       <c r="Q13">
-        <v>794.1227100750001</v>
+        <v>791.1725019</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07618043714120332</v>
+        <v>0.07644668308483385</v>
       </c>
       <c r="T13">
-        <v>0.6089351520179661</v>
+        <v>0.6142716951824142</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.51066756038788</v>
+        <v>21.55144526368889</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07180008111465379</v>
+        <v>0.07164982317363663</v>
       </c>
       <c r="C14">
-        <v>7321.179862388892</v>
+        <v>7282.352942250523</v>
       </c>
       <c r="D14">
-        <v>6774.115862388892</v>
+        <v>6813.491942250524</v>
       </c>
       <c r="E14">
-        <v>938.436</v>
+        <v>1016.639</v>
       </c>
       <c r="F14">
-        <v>938.436</v>
+        <v>1016.639</v>
       </c>
       <c r="G14">
         <v>1485.5</v>
@@ -2441,28 +2441,28 @@
         <v>1017.3</v>
       </c>
       <c r="M14">
-        <v>47.2033308</v>
+        <v>51.1369417</v>
       </c>
       <c r="N14">
-        <v>970.0966692000001</v>
+        <v>966.1630583000001</v>
       </c>
       <c r="O14">
-        <v>242.5241673</v>
+        <v>241.540764575</v>
       </c>
       <c r="P14">
-        <v>727.5725019</v>
+        <v>724.6222937250001</v>
       </c>
       <c r="Q14">
-        <v>791.1725019</v>
+        <v>788.2222937250001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07644668308483385</v>
+        <v>0.0767190496248697</v>
       </c>
       <c r="T14">
-        <v>0.6142716951824142</v>
+        <v>0.619730917500068</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.55144526368889</v>
+        <v>19.89364178186667</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07164982317363663</v>
+        <v>0.07149956523261948</v>
       </c>
       <c r="C15">
-        <v>7282.352942250523</v>
+        <v>7243.986463262176</v>
       </c>
       <c r="D15">
-        <v>6813.491942250524</v>
+        <v>6853.328463262175</v>
       </c>
       <c r="E15">
-        <v>1016.639</v>
+        <v>1094.842</v>
       </c>
       <c r="F15">
-        <v>1016.639</v>
+        <v>1094.842</v>
       </c>
       <c r="G15">
         <v>1485.5</v>
@@ -2523,28 +2523,28 @@
         <v>1017.3</v>
       </c>
       <c r="M15">
-        <v>51.1369417</v>
+        <v>55.0705526</v>
       </c>
       <c r="N15">
-        <v>966.1630583000001</v>
+        <v>962.2294474</v>
       </c>
       <c r="O15">
-        <v>241.540764575</v>
+        <v>240.55736185</v>
       </c>
       <c r="P15">
-        <v>724.6222937250001</v>
+        <v>721.67208555</v>
       </c>
       <c r="Q15">
-        <v>788.2222937250001</v>
+        <v>785.27208555</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0767190496248697</v>
+        <v>0.07699775027048777</v>
       </c>
       <c r="T15">
-        <v>0.619730917500068</v>
+        <v>0.625317098476272</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.89364178186667</v>
+        <v>18.47266736887619</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07149956523261948</v>
+        <v>0.07134930729160235</v>
       </c>
       <c r="C16">
-        <v>7243.986463262176</v>
+        <v>7206.088549120306</v>
       </c>
       <c r="D16">
-        <v>6853.328463262175</v>
+        <v>6893.633549120307</v>
       </c>
       <c r="E16">
-        <v>1094.842</v>
+        <v>1173.045</v>
       </c>
       <c r="F16">
-        <v>1094.842</v>
+        <v>1173.045</v>
       </c>
       <c r="G16">
         <v>1485.5</v>
@@ -2605,28 +2605,28 @@
         <v>1017.3</v>
       </c>
       <c r="M16">
-        <v>55.0705526</v>
+        <v>59.00416350000001</v>
       </c>
       <c r="N16">
-        <v>962.2294474</v>
+        <v>958.2958365000001</v>
       </c>
       <c r="O16">
-        <v>240.55736185</v>
+        <v>239.573959125</v>
       </c>
       <c r="P16">
-        <v>721.67208555</v>
+        <v>718.7218773750001</v>
       </c>
       <c r="Q16">
-        <v>785.27208555</v>
+        <v>782.3218773750001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07699775027048777</v>
+        <v>0.07728300857835571</v>
       </c>
       <c r="T16">
-        <v>0.625317098476272</v>
+        <v>0.6310347190048573</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.47266736887619</v>
+        <v>17.24115621095111</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07134930729160235</v>
+        <v>0.07119904935058519</v>
       </c>
       <c r="C17">
-        <v>7206.088549120306</v>
+        <v>7168.667515756937</v>
       </c>
       <c r="D17">
-        <v>6893.633549120307</v>
+        <v>6934.415515756937</v>
       </c>
       <c r="E17">
-        <v>1173.045</v>
+        <v>1251.248</v>
       </c>
       <c r="F17">
-        <v>1173.045</v>
+        <v>1251.248</v>
       </c>
       <c r="G17">
         <v>1485.5</v>
@@ -2687,28 +2687,28 @@
         <v>1017.3</v>
       </c>
       <c r="M17">
-        <v>59.0041635</v>
+        <v>62.9377744</v>
       </c>
       <c r="N17">
-        <v>958.2958365000001</v>
+        <v>954.3622256000001</v>
       </c>
       <c r="O17">
-        <v>239.573959125</v>
+        <v>238.5905564</v>
       </c>
       <c r="P17">
-        <v>718.7218773750001</v>
+        <v>715.7716692000001</v>
       </c>
       <c r="Q17">
-        <v>782.3218773750001</v>
+        <v>779.3716692000002</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07728300857835571</v>
+        <v>0.07757505875069666</v>
       </c>
       <c r="T17">
-        <v>0.6310347190048573</v>
+        <v>0.6368884733555517</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.24115621095111</v>
+        <v>16.16358394776667</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07119904935058519</v>
+        <v>0.07104879140956803</v>
       </c>
       <c r="C18">
-        <v>7168.667515756937</v>
+        <v>7131.731877059633</v>
       </c>
       <c r="D18">
-        <v>6934.415515756937</v>
+        <v>6975.682877059632</v>
       </c>
       <c r="E18">
-        <v>1251.248</v>
+        <v>1329.451</v>
       </c>
       <c r="F18">
-        <v>1251.248</v>
+        <v>1329.451</v>
       </c>
       <c r="G18">
         <v>1485.5</v>
@@ -2769,28 +2769,28 @@
         <v>1017.3</v>
       </c>
       <c r="M18">
-        <v>62.9377744</v>
+        <v>66.8713853</v>
       </c>
       <c r="N18">
-        <v>954.3622256000001</v>
+        <v>950.4286147</v>
       </c>
       <c r="O18">
-        <v>238.5905564</v>
+        <v>237.607153675</v>
       </c>
       <c r="P18">
-        <v>715.7716692000001</v>
+        <v>712.821461025</v>
       </c>
       <c r="Q18">
-        <v>779.3716692000002</v>
+        <v>776.421461025</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07757505875069666</v>
+        <v>0.07787414627658801</v>
       </c>
       <c r="T18">
-        <v>0.6368884733555517</v>
+        <v>0.6428832820279496</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.16358394776667</v>
+        <v>15.21278489201569</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07104879140956803</v>
+        <v>0.07089853346855089</v>
       </c>
       <c r="C19">
-        <v>7131.731877059633</v>
+        <v>7095.290350797086</v>
       </c>
       <c r="D19">
-        <v>6975.682877059632</v>
+        <v>7017.444350797087</v>
       </c>
       <c r="E19">
-        <v>1329.451</v>
+        <v>1407.654</v>
       </c>
       <c r="F19">
-        <v>1329.451</v>
+        <v>1407.654</v>
       </c>
       <c r="G19">
         <v>1485.5</v>
@@ -2851,28 +2851,28 @@
         <v>1017.3</v>
       </c>
       <c r="M19">
-        <v>66.8713853</v>
+        <v>70.80499620000001</v>
       </c>
       <c r="N19">
-        <v>950.4286147</v>
+        <v>946.4950038000001</v>
       </c>
       <c r="O19">
-        <v>237.607153675</v>
+        <v>236.62375095</v>
       </c>
       <c r="P19">
-        <v>712.821461025</v>
+        <v>709.87125285</v>
       </c>
       <c r="Q19">
-        <v>776.421461025</v>
+        <v>773.47125285</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07787414627658801</v>
+        <v>0.07818052862018401</v>
       </c>
       <c r="T19">
-        <v>0.6428832820279496</v>
+        <v>0.6490243055460158</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.21278489201569</v>
+        <v>14.36763017579259</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07089853346855091</v>
+        <v>0.07074827552753375</v>
       </c>
       <c r="C20">
-        <v>7095.290350797082</v>
+        <v>7059.351864758759</v>
       </c>
       <c r="D20">
-        <v>7017.444350797084</v>
+        <v>7059.70886475876</v>
       </c>
       <c r="E20">
-        <v>1407.654</v>
+        <v>1485.857</v>
       </c>
       <c r="F20">
-        <v>1407.654</v>
+        <v>1485.857</v>
       </c>
       <c r="G20">
         <v>1485.5</v>
@@ -2933,28 +2933,28 @@
         <v>1017.3</v>
       </c>
       <c r="M20">
-        <v>70.80499619999999</v>
+        <v>74.7386071</v>
       </c>
       <c r="N20">
-        <v>946.4950038000001</v>
+        <v>942.5613929000001</v>
       </c>
       <c r="O20">
-        <v>236.62375095</v>
+        <v>235.640348225</v>
       </c>
       <c r="P20">
-        <v>709.87125285</v>
+        <v>706.9210446750001</v>
       </c>
       <c r="Q20">
-        <v>773.47125285</v>
+        <v>770.5210446750001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07818052862018401</v>
+        <v>0.07849447595991821</v>
       </c>
       <c r="T20">
-        <v>0.6490243055460158</v>
+        <v>0.6553169592744046</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.3676301757926</v>
+        <v>13.61143911390878</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07074827552753375</v>
+        <v>0.0705980175865166</v>
       </c>
       <c r="C21">
-        <v>7059.351864758759</v>
+        <v>7023.925563117745</v>
       </c>
       <c r="D21">
-        <v>7059.70886475876</v>
+        <v>7102.485563117744</v>
       </c>
       <c r="E21">
-        <v>1485.857</v>
+        <v>1564.06</v>
       </c>
       <c r="F21">
-        <v>1485.857</v>
+        <v>1564.06</v>
       </c>
       <c r="G21">
         <v>1485.5</v>
@@ -3015,28 +3015,28 @@
         <v>1017.3</v>
       </c>
       <c r="M21">
-        <v>74.7386071</v>
+        <v>78.672218</v>
       </c>
       <c r="N21">
-        <v>942.5613929000001</v>
+        <v>938.627782</v>
       </c>
       <c r="O21">
-        <v>235.640348225</v>
+        <v>234.6569455</v>
       </c>
       <c r="P21">
-        <v>706.9210446750001</v>
+        <v>703.9708365</v>
       </c>
       <c r="Q21">
-        <v>770.5210446750001</v>
+        <v>767.5708365</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07849447595991821</v>
+        <v>0.07881627198314575</v>
       </c>
       <c r="T21">
-        <v>0.6553169592744046</v>
+        <v>0.661766929346003</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>13.61143911390878</v>
+        <v>12.93086715821333</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0705980175865166</v>
+        <v>0.07044775964549946</v>
       </c>
       <c r="C22">
-        <v>7023.925563117745</v>
+        <v>6989.020813026348</v>
       </c>
       <c r="D22">
-        <v>7102.485563117744</v>
+        <v>7145.783813026349</v>
       </c>
       <c r="E22">
-        <v>1564.06</v>
+        <v>1642.263</v>
       </c>
       <c r="F22">
-        <v>1564.06</v>
+        <v>1642.263</v>
       </c>
       <c r="G22">
         <v>1485.5</v>
@@ -3097,28 +3097,28 @@
         <v>1017.3</v>
       </c>
       <c r="M22">
-        <v>78.672218</v>
+        <v>82.60582890000001</v>
       </c>
       <c r="N22">
-        <v>938.627782</v>
+        <v>934.6941711000001</v>
       </c>
       <c r="O22">
-        <v>234.6569455</v>
+        <v>233.673542775</v>
       </c>
       <c r="P22">
-        <v>703.9708365</v>
+        <v>701.0206283250001</v>
       </c>
       <c r="Q22">
-        <v>767.5708365</v>
+        <v>764.6206283250001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07881627198314575</v>
+        <v>0.07914621474113855</v>
       </c>
       <c r="T22">
-        <v>0.661766929346003</v>
+        <v>0.6683801897991609</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.93086715821333</v>
+        <v>12.31511157925079</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07044775964549946</v>
+        <v>0.0702975017044823</v>
       </c>
       <c r="C23">
-        <v>6989.020813026348</v>
+        <v>6954.647211454458</v>
       </c>
       <c r="D23">
-        <v>7145.783813026349</v>
+        <v>7189.613211454458</v>
       </c>
       <c r="E23">
-        <v>1642.263</v>
+        <v>1720.466</v>
       </c>
       <c r="F23">
-        <v>1642.263</v>
+        <v>1720.466</v>
       </c>
       <c r="G23">
         <v>1485.5</v>
@@ -3179,28 +3179,28 @@
         <v>1017.3</v>
       </c>
       <c r="M23">
-        <v>82.60582889999999</v>
+        <v>86.5394398</v>
       </c>
       <c r="N23">
-        <v>934.6941711000001</v>
+        <v>930.7605602000001</v>
       </c>
       <c r="O23">
-        <v>233.673542775</v>
+        <v>232.69014005</v>
       </c>
       <c r="P23">
-        <v>701.0206283250001</v>
+        <v>698.07042015</v>
       </c>
       <c r="Q23">
-        <v>764.6206283250001</v>
+        <v>761.67042015</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07914621474113855</v>
+        <v>0.07948461756984911</v>
       </c>
       <c r="T23">
-        <v>0.6683801897991609</v>
+        <v>0.6751630210331689</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>12.3151115792508</v>
+        <v>11.75533378019394</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0702975017044823</v>
+        <v>0.07014724376346516</v>
       </c>
       <c r="C24">
-        <v>6954.647211454458</v>
+        <v>6920.814592281049</v>
       </c>
       <c r="D24">
-        <v>7189.613211454458</v>
+        <v>7233.983592281049</v>
       </c>
       <c r="E24">
-        <v>1720.466</v>
+        <v>1798.669</v>
       </c>
       <c r="F24">
-        <v>1720.466</v>
+        <v>1798.669</v>
       </c>
       <c r="G24">
         <v>1485.5</v>
@@ -3261,28 +3261,28 @@
         <v>1017.3</v>
       </c>
       <c r="M24">
-        <v>86.5394398</v>
+        <v>90.4730507</v>
       </c>
       <c r="N24">
-        <v>930.7605602000001</v>
+        <v>926.8269493</v>
       </c>
       <c r="O24">
-        <v>232.69014005</v>
+        <v>231.706737325</v>
       </c>
       <c r="P24">
-        <v>698.07042015</v>
+        <v>695.1202119750001</v>
       </c>
       <c r="Q24">
-        <v>761.67042015</v>
+        <v>758.7202119750001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07948461756984911</v>
+        <v>0.07983181008242228</v>
       </c>
       <c r="T24">
-        <v>0.6751630210331689</v>
+        <v>0.6821220297018267</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.75533378019394</v>
+        <v>11.24423231148986</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07014724376346516</v>
+        <v>0.06999698582244801</v>
       </c>
       <c r="C25">
-        <v>6920.814592281049</v>
+        <v>6887.533033649982</v>
       </c>
       <c r="D25">
-        <v>7233.983592281049</v>
+        <v>7278.905033649982</v>
       </c>
       <c r="E25">
-        <v>1798.669</v>
+        <v>1876.872</v>
       </c>
       <c r="F25">
-        <v>1798.669</v>
+        <v>1876.872</v>
       </c>
       <c r="G25">
         <v>1485.5</v>
@@ -3343,28 +3343,28 @@
         <v>1017.3</v>
       </c>
       <c r="M25">
-        <v>90.4730507</v>
+        <v>94.40666160000001</v>
       </c>
       <c r="N25">
-        <v>926.8269493</v>
+        <v>922.8933384000001</v>
       </c>
       <c r="O25">
-        <v>231.706737325</v>
+        <v>230.7233346</v>
       </c>
       <c r="P25">
-        <v>695.1202119750001</v>
+        <v>692.1700038</v>
       </c>
       <c r="Q25">
-        <v>758.7202119750001</v>
+        <v>755.7700038</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07983181008242228</v>
+        <v>0.08018813924006317</v>
       </c>
       <c r="T25">
-        <v>0.6821220297018267</v>
+        <v>0.6892641701775544</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.24423231148986</v>
+        <v>10.77572263184445</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06999698582244801</v>
+        <v>0.06984672788143086</v>
       </c>
       <c r="C26">
-        <v>6887.533033649982</v>
+        <v>6854.812865601526</v>
       </c>
       <c r="D26">
-        <v>7278.905033649982</v>
+        <v>7324.387865601527</v>
       </c>
       <c r="E26">
-        <v>1876.872</v>
+        <v>1955.075</v>
       </c>
       <c r="F26">
-        <v>1876.872</v>
+        <v>1955.075</v>
       </c>
       <c r="G26">
         <v>1485.5</v>
@@ -3425,28 +3425,28 @@
         <v>1017.3</v>
       </c>
       <c r="M26">
-        <v>94.40666159999999</v>
+        <v>98.3402725</v>
       </c>
       <c r="N26">
-        <v>922.8933384000001</v>
+        <v>918.9597275000001</v>
       </c>
       <c r="O26">
-        <v>230.7233346</v>
+        <v>229.739931875</v>
       </c>
       <c r="P26">
-        <v>692.1700038</v>
+        <v>689.2197956250001</v>
       </c>
       <c r="Q26">
-        <v>755.7700038</v>
+        <v>752.8197956250001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08018813924006317</v>
+        <v>0.08055397050857448</v>
       </c>
       <c r="T26">
-        <v>0.6892641701775544</v>
+        <v>0.6965967677326347</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.77572263184445</v>
+        <v>10.34469372657067</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06984672788143086</v>
+        <v>0.06969646994041372</v>
       </c>
       <c r="C27">
-        <v>6854.812865601526</v>
+        <v>6822.664677991828</v>
       </c>
       <c r="D27">
-        <v>7324.387865601527</v>
+        <v>7370.442677991828</v>
       </c>
       <c r="E27">
-        <v>1955.075</v>
+        <v>2033.278</v>
       </c>
       <c r="F27">
-        <v>1955.075</v>
+        <v>2033.278</v>
       </c>
       <c r="G27">
         <v>1485.5</v>
@@ -3507,28 +3507,28 @@
         <v>1017.3</v>
       </c>
       <c r="M27">
-        <v>98.3402725</v>
+        <v>102.2738834</v>
       </c>
       <c r="N27">
-        <v>918.9597275000001</v>
+        <v>915.0261166</v>
       </c>
       <c r="O27">
-        <v>229.739931875</v>
+        <v>228.75652915</v>
       </c>
       <c r="P27">
-        <v>689.2197956250001</v>
+        <v>686.26958745</v>
       </c>
       <c r="Q27">
-        <v>752.8197956250001</v>
+        <v>749.86958745</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08055397050857448</v>
+        <v>0.08092968910866719</v>
       </c>
       <c r="T27">
-        <v>0.6965967677326347</v>
+        <v>0.7041275436000146</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.34469372657067</v>
+        <v>9.946820890933335</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06969646994041372</v>
+        <v>0.06954621199939655</v>
       </c>
       <c r="C28">
-        <v>6822.664677991828</v>
+        <v>6791.099328713055</v>
       </c>
       <c r="D28">
-        <v>7370.442677991828</v>
+        <v>7417.080328713056</v>
       </c>
       <c r="E28">
-        <v>2033.278</v>
+        <v>2111.481</v>
       </c>
       <c r="F28">
-        <v>2033.278</v>
+        <v>2111.481</v>
       </c>
       <c r="G28">
         <v>1485.5</v>
@@ -3589,28 +3589,28 @@
         <v>1017.3</v>
       </c>
       <c r="M28">
-        <v>102.2738834</v>
+        <v>106.2074943</v>
       </c>
       <c r="N28">
-        <v>915.0261166</v>
+        <v>911.0925057000001</v>
       </c>
       <c r="O28">
-        <v>228.75652915</v>
+        <v>227.773126425</v>
       </c>
       <c r="P28">
-        <v>686.26958745</v>
+        <v>683.3193792750001</v>
       </c>
       <c r="Q28">
-        <v>749.86958745</v>
+        <v>746.9193792750001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08092968910866719</v>
+        <v>0.08131570136903638</v>
       </c>
       <c r="T28">
-        <v>0.7041275436000146</v>
+        <v>0.711864642093898</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.946820890933335</v>
+        <v>9.578420117195064</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06954621199939655</v>
+        <v>0.06939595405837941</v>
       </c>
       <c r="C29">
-        <v>6791.099328713055</v>
+        <v>6760.12795222757</v>
       </c>
       <c r="D29">
-        <v>7417.080328713056</v>
+        <v>7464.311952227571</v>
       </c>
       <c r="E29">
-        <v>2111.481</v>
+        <v>2189.684</v>
       </c>
       <c r="F29">
-        <v>2111.481</v>
+        <v>2189.684</v>
       </c>
       <c r="G29">
         <v>1485.5</v>
@@ -3671,28 +3671,28 @@
         <v>1017.3</v>
       </c>
       <c r="M29">
-        <v>106.2074943</v>
+        <v>110.1411052</v>
       </c>
       <c r="N29">
-        <v>911.0925057000001</v>
+        <v>907.1588948000001</v>
       </c>
       <c r="O29">
-        <v>227.773126425</v>
+        <v>226.7897237</v>
       </c>
       <c r="P29">
-        <v>683.3193792750001</v>
+        <v>680.3691711000001</v>
       </c>
       <c r="Q29">
-        <v>746.9193792750001</v>
+        <v>743.9691711000002</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08131570136903638</v>
+        <v>0.08171243619219362</v>
       </c>
       <c r="T29">
-        <v>0.711864642093898</v>
+        <v>0.7198166599903892</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.578420117195064</v>
+        <v>9.236333684438097</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06939595405837941</v>
+        <v>0.06924569611736225</v>
       </c>
       <c r="C30">
-        <v>6760.12795222757</v>
+        <v>6729.761968430339</v>
       </c>
       <c r="D30">
-        <v>7464.311952227571</v>
+        <v>7512.14896843034</v>
       </c>
       <c r="E30">
-        <v>2189.684</v>
+        <v>2267.887</v>
       </c>
       <c r="F30">
-        <v>2189.684</v>
+        <v>2267.887</v>
       </c>
       <c r="G30">
         <v>1485.5</v>
@@ -3753,28 +3753,28 @@
         <v>1017.3</v>
       </c>
       <c r="M30">
-        <v>110.1411052</v>
+        <v>114.0747161</v>
       </c>
       <c r="N30">
-        <v>907.1588948000001</v>
+        <v>903.2252839</v>
       </c>
       <c r="O30">
-        <v>226.7897237</v>
+        <v>225.806320975</v>
       </c>
       <c r="P30">
-        <v>680.3691711000001</v>
+        <v>677.418962925</v>
       </c>
       <c r="Q30">
-        <v>743.9691711000002</v>
+        <v>741.018962925</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08171243619219362</v>
+        <v>0.0821203466441722</v>
       </c>
       <c r="T30">
-        <v>0.7198166599903892</v>
+        <v>0.7279926783910069</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.236333684438097</v>
+        <v>8.917839419457472</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06924569611736225</v>
+        <v>0.0694329381763451</v>
       </c>
       <c r="C31">
-        <v>6729.76196843034</v>
+        <v>6592.040755767188</v>
       </c>
       <c r="D31">
-        <v>7512.14896843034</v>
+        <v>7452.630755767188</v>
       </c>
       <c r="E31">
-        <v>2267.887</v>
+        <v>2346.09</v>
       </c>
       <c r="F31">
-        <v>2267.887</v>
+        <v>2346.09</v>
       </c>
       <c r="G31">
         <v>1485.5</v>
@@ -3835,45 +3835,45 @@
         <v>1017.3</v>
       </c>
       <c r="M31">
-        <v>114.0747161</v>
+        <v>121.527462</v>
       </c>
       <c r="N31">
-        <v>903.2252839000001</v>
+        <v>895.7725380000001</v>
       </c>
       <c r="O31">
-        <v>225.806320975</v>
+        <v>223.9431345</v>
       </c>
       <c r="P31">
-        <v>677.4189629250001</v>
+        <v>671.8294035</v>
       </c>
       <c r="Q31">
-        <v>741.0189629250001</v>
+        <v>735.4294035</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0821203466441722</v>
+        <v>0.08253991168049302</v>
       </c>
       <c r="T31">
-        <v>0.7279926783910069</v>
+        <v>0.7364022973173566</v>
       </c>
       <c r="U31">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y31">
-        <v>8.917839419457476</v>
+        <v>8.370947465355609</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0694329381763451</v>
+        <v>0.06929393023532796</v>
       </c>
       <c r="C32">
-        <v>6592.040755767188</v>
+        <v>6557.933181527946</v>
       </c>
       <c r="D32">
-        <v>7452.630755767188</v>
+        <v>7496.726181527944</v>
       </c>
       <c r="E32">
-        <v>2346.09</v>
+        <v>2424.293</v>
       </c>
       <c r="F32">
-        <v>2346.09</v>
+        <v>2424.293</v>
       </c>
       <c r="G32">
         <v>1485.5</v>
@@ -3917,28 +3917,28 @@
         <v>1017.3</v>
       </c>
       <c r="M32">
-        <v>121.527462</v>
+        <v>125.5783774</v>
       </c>
       <c r="N32">
-        <v>895.7725380000001</v>
+        <v>891.7216226</v>
       </c>
       <c r="O32">
-        <v>223.9431345</v>
+        <v>222.93040565</v>
       </c>
       <c r="P32">
-        <v>671.8294035</v>
+        <v>668.79121695</v>
       </c>
       <c r="Q32">
-        <v>735.4294035</v>
+        <v>732.3912169500001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08253991168049302</v>
+        <v>0.08297163802221444</v>
       </c>
       <c r="T32">
-        <v>0.7364022973173566</v>
+        <v>0.7450556733140353</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.370947465355609</v>
+        <v>8.10091690195704</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06929393023532796</v>
+        <v>0.06915492229431081</v>
       </c>
       <c r="C33">
-        <v>6557.933181527946</v>
+        <v>6524.350517135629</v>
       </c>
       <c r="D33">
-        <v>7496.726181527944</v>
+        <v>7541.34651713563</v>
       </c>
       <c r="E33">
-        <v>2424.293</v>
+        <v>2502.496</v>
       </c>
       <c r="F33">
-        <v>2424.293</v>
+        <v>2502.496</v>
       </c>
       <c r="G33">
         <v>1485.5</v>
@@ -3999,28 +3999,28 @@
         <v>1017.3</v>
       </c>
       <c r="M33">
-        <v>125.5783774</v>
+        <v>129.6292928</v>
       </c>
       <c r="N33">
-        <v>891.7216226</v>
+        <v>887.6707072</v>
       </c>
       <c r="O33">
-        <v>222.93040565</v>
+        <v>221.9176768</v>
       </c>
       <c r="P33">
-        <v>668.79121695</v>
+        <v>665.7530304000001</v>
       </c>
       <c r="Q33">
-        <v>732.3912169500001</v>
+        <v>729.3530304000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08297163802221444</v>
+        <v>0.08341606219751591</v>
       </c>
       <c r="T33">
-        <v>0.7450556733140353</v>
+        <v>0.75396356036944</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.10091690195704</v>
+        <v>7.847763248770883</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06915492229431081</v>
+        <v>0.06901591435329366</v>
       </c>
       <c r="C34">
-        <v>6524.350517135629</v>
+        <v>6491.302191463379</v>
       </c>
       <c r="D34">
-        <v>7541.34651713563</v>
+        <v>7586.501191463379</v>
       </c>
       <c r="E34">
-        <v>2502.496</v>
+        <v>2580.699</v>
       </c>
       <c r="F34">
-        <v>2502.496</v>
+        <v>2580.699</v>
       </c>
       <c r="G34">
         <v>1485.5</v>
@@ -4081,28 +4081,28 @@
         <v>1017.3</v>
       </c>
       <c r="M34">
-        <v>129.6292928</v>
+        <v>133.6802082</v>
       </c>
       <c r="N34">
-        <v>887.6707072</v>
+        <v>883.6197918</v>
       </c>
       <c r="O34">
-        <v>221.9176768</v>
+        <v>220.90494795</v>
       </c>
       <c r="P34">
-        <v>665.7530304000001</v>
+        <v>662.7148438500001</v>
       </c>
       <c r="Q34">
-        <v>729.3530304000001</v>
+        <v>726.3148438500001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08341606219751591</v>
+        <v>0.08387375276610995</v>
       </c>
       <c r="T34">
-        <v>0.75396356036944</v>
+        <v>0.7631373545011253</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.847763248770883</v>
+        <v>7.609952241232371</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06901591435329366</v>
+        <v>0.06887690641227651</v>
       </c>
       <c r="C35">
-        <v>6491.302191463379</v>
+        <v>6458.79786057045</v>
       </c>
       <c r="D35">
-        <v>7586.501191463379</v>
+        <v>7632.19986057045</v>
       </c>
       <c r="E35">
-        <v>2580.699</v>
+        <v>2658.902</v>
       </c>
       <c r="F35">
-        <v>2580.699</v>
+        <v>2658.902</v>
       </c>
       <c r="G35">
         <v>1485.5</v>
@@ -4163,28 +4163,28 @@
         <v>1017.3</v>
       </c>
       <c r="M35">
-        <v>133.6802082</v>
+        <v>137.7311236</v>
       </c>
       <c r="N35">
-        <v>883.6197918</v>
+        <v>879.5688764000001</v>
       </c>
       <c r="O35">
-        <v>220.90494795</v>
+        <v>219.8922191</v>
       </c>
       <c r="P35">
-        <v>662.7148438500001</v>
+        <v>659.6766573000001</v>
       </c>
       <c r="Q35">
-        <v>726.3148438500001</v>
+        <v>723.2766573000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08387375276610995</v>
+        <v>0.08434531274587351</v>
       </c>
       <c r="T35">
-        <v>0.7631373545011253</v>
+        <v>0.7725891423943767</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.609952241232371</v>
+        <v>7.386130116490244</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06887690641227651</v>
+        <v>0.06873789847125936</v>
       </c>
       <c r="C36">
-        <v>6458.79786057045</v>
+        <v>6426.847414586179</v>
       </c>
       <c r="D36">
-        <v>7632.19986057045</v>
+        <v>7678.452414586181</v>
       </c>
       <c r="E36">
-        <v>2658.902</v>
+        <v>2737.105</v>
       </c>
       <c r="F36">
-        <v>2658.902</v>
+        <v>2737.105</v>
       </c>
       <c r="G36">
         <v>1485.5</v>
@@ -4245,28 +4245,28 @@
         <v>1017.3</v>
       </c>
       <c r="M36">
-        <v>137.7311236</v>
+        <v>141.782039</v>
       </c>
       <c r="N36">
-        <v>879.5688764000001</v>
+        <v>875.517961</v>
       </c>
       <c r="O36">
-        <v>219.8922191</v>
+        <v>218.87949025</v>
       </c>
       <c r="P36">
-        <v>659.6766573000001</v>
+        <v>656.63847075</v>
       </c>
       <c r="Q36">
-        <v>723.2766573000001</v>
+        <v>720.23847075</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08434531274587351</v>
+        <v>0.08483138226347595</v>
       </c>
       <c r="T36">
-        <v>0.7725891423943767</v>
+        <v>0.7823317545304975</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.386130116490244</v>
+        <v>7.175097827447663</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06873789847125936</v>
+        <v>0.06859889053024222</v>
       </c>
       <c r="C37">
-        <v>6426.847414586179</v>
+        <v>6395.460984845766</v>
       </c>
       <c r="D37">
-        <v>7678.452414586181</v>
+        <v>7725.268984845767</v>
       </c>
       <c r="E37">
-        <v>2737.105</v>
+        <v>2815.308</v>
       </c>
       <c r="F37">
-        <v>2737.105</v>
+        <v>2815.308</v>
       </c>
       <c r="G37">
         <v>1485.5</v>
@@ -4327,28 +4327,28 @@
         <v>1017.3</v>
       </c>
       <c r="M37">
-        <v>141.782039</v>
+        <v>145.8329544</v>
       </c>
       <c r="N37">
-        <v>875.517961</v>
+        <v>871.4670456</v>
       </c>
       <c r="O37">
-        <v>218.87949025</v>
+        <v>217.8667614</v>
       </c>
       <c r="P37">
-        <v>656.63847075</v>
+        <v>653.6002842</v>
       </c>
       <c r="Q37">
-        <v>720.23847075</v>
+        <v>717.2002842000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08483138226347595</v>
+        <v>0.08533264145350347</v>
       </c>
       <c r="T37">
-        <v>0.7823317545304975</v>
+        <v>0.7923788232958719</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.175097827447663</v>
+        <v>6.975789554463006</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06859889053024222</v>
+        <v>0.06845988258922506</v>
       </c>
       <c r="C38">
-        <v>6395.460984845767</v>
+        <v>6364.648951288716</v>
       </c>
       <c r="D38">
-        <v>7725.268984845767</v>
+        <v>7772.659951288717</v>
       </c>
       <c r="E38">
-        <v>2815.308</v>
+        <v>2893.511</v>
       </c>
       <c r="F38">
-        <v>2815.308</v>
+        <v>2893.511</v>
       </c>
       <c r="G38">
         <v>1485.5</v>
@@ -4409,28 +4409,28 @@
         <v>1017.3</v>
       </c>
       <c r="M38">
-        <v>145.8329544</v>
+        <v>149.8838698</v>
       </c>
       <c r="N38">
-        <v>871.4670456000001</v>
+        <v>867.4161302000001</v>
       </c>
       <c r="O38">
-        <v>217.8667614</v>
+        <v>216.85403255</v>
       </c>
       <c r="P38">
-        <v>653.6002842</v>
+        <v>650.5620976500001</v>
       </c>
       <c r="Q38">
-        <v>717.2002842000001</v>
+        <v>714.1620976500001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08533264145350347</v>
+        <v>0.08584981363369058</v>
       </c>
       <c r="T38">
-        <v>0.7923788232958719</v>
+        <v>0.8027448466252266</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.975789554463008</v>
+        <v>6.787254701639684</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06845988258922506</v>
+        <v>0.06880537464820792</v>
       </c>
       <c r="C39">
-        <v>6364.648951288716</v>
+        <v>6169.717042005184</v>
       </c>
       <c r="D39">
-        <v>7772.659951288717</v>
+        <v>7655.931042005183</v>
       </c>
       <c r="E39">
-        <v>2893.511</v>
+        <v>2971.714</v>
       </c>
       <c r="F39">
-        <v>2893.511</v>
+        <v>2971.714</v>
       </c>
       <c r="G39">
         <v>1485.5</v>
@@ -4491,45 +4491,45 @@
         <v>1017.3</v>
       </c>
       <c r="M39">
-        <v>149.8838698</v>
+        <v>158.986699</v>
       </c>
       <c r="N39">
-        <v>867.4161302000001</v>
+        <v>858.3133010000001</v>
       </c>
       <c r="O39">
-        <v>216.85403255</v>
+        <v>214.57832525</v>
       </c>
       <c r="P39">
-        <v>650.5620976500001</v>
+        <v>643.7349757500001</v>
       </c>
       <c r="Q39">
-        <v>714.1620976500001</v>
+        <v>707.3349757500001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08584981363369058</v>
+        <v>0.08638366878743213</v>
       </c>
       <c r="T39">
-        <v>0.8027448466252266</v>
+        <v>0.8134452578039154</v>
       </c>
       <c r="U39">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>6.787254701639684</v>
+        <v>6.398648480650574</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06880537464820792</v>
+        <v>0.06867911670719076</v>
       </c>
       <c r="C40">
-        <v>6169.717042005184</v>
+        <v>6133.763142016508</v>
       </c>
       <c r="D40">
-        <v>7655.931042005183</v>
+        <v>7698.180142016508</v>
       </c>
       <c r="E40">
-        <v>2971.714</v>
+        <v>3049.917</v>
       </c>
       <c r="F40">
-        <v>2971.714</v>
+        <v>3049.917</v>
       </c>
       <c r="G40">
         <v>1485.5</v>
@@ -4573,28 +4573,28 @@
         <v>1017.3</v>
       </c>
       <c r="M40">
-        <v>158.986699</v>
+        <v>163.1705595</v>
       </c>
       <c r="N40">
-        <v>858.3133010000001</v>
+        <v>854.1294405000001</v>
       </c>
       <c r="O40">
-        <v>214.57832525</v>
+        <v>213.532360125</v>
       </c>
       <c r="P40">
-        <v>643.7349757500001</v>
+        <v>640.5970803750001</v>
       </c>
       <c r="Q40">
-        <v>707.3349757500001</v>
+        <v>704.1970803750002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08638366878743213</v>
+        <v>0.08693502738883732</v>
       </c>
       <c r="T40">
-        <v>0.8134452578039154</v>
+        <v>0.8244965021360037</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.398648480650574</v>
+        <v>6.234580570890301</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06867911670719076</v>
+        <v>0.06855285876617362</v>
       </c>
       <c r="C41">
-        <v>6133.763142016508</v>
+        <v>6098.278131184317</v>
       </c>
       <c r="D41">
-        <v>7698.180142016508</v>
+        <v>7740.898131184318</v>
       </c>
       <c r="E41">
-        <v>3049.917</v>
+        <v>3128.12</v>
       </c>
       <c r="F41">
-        <v>3049.917</v>
+        <v>3128.12</v>
       </c>
       <c r="G41">
         <v>1485.5</v>
@@ -4655,28 +4655,28 @@
         <v>1017.3</v>
       </c>
       <c r="M41">
-        <v>163.1705595</v>
+        <v>167.35442</v>
       </c>
       <c r="N41">
-        <v>854.1294405000001</v>
+        <v>849.9455800000001</v>
       </c>
       <c r="O41">
-        <v>213.532360125</v>
+        <v>212.486395</v>
       </c>
       <c r="P41">
-        <v>640.5970803750001</v>
+        <v>637.459185</v>
       </c>
       <c r="Q41">
-        <v>704.1970803750002</v>
+        <v>701.0591850000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08693502738883732</v>
+        <v>0.08750476461028937</v>
       </c>
       <c r="T41">
-        <v>0.8244965021360037</v>
+        <v>0.8359161212791617</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.234580570890301</v>
+        <v>6.078716056618044</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06855285876617362</v>
+        <v>0.06842660082515648</v>
       </c>
       <c r="C42">
-        <v>6098.278131184317</v>
+        <v>6063.269858806867</v>
       </c>
       <c r="D42">
-        <v>7740.898131184318</v>
+        <v>7784.092858806867</v>
       </c>
       <c r="E42">
-        <v>3128.12</v>
+        <v>3206.323</v>
       </c>
       <c r="F42">
-        <v>3128.12</v>
+        <v>3206.323</v>
       </c>
       <c r="G42">
         <v>1485.5</v>
@@ -4737,28 +4737,28 @@
         <v>1017.3</v>
       </c>
       <c r="M42">
-        <v>167.35442</v>
+        <v>171.5382805</v>
       </c>
       <c r="N42">
-        <v>849.9455800000001</v>
+        <v>845.7617195</v>
       </c>
       <c r="O42">
-        <v>212.486395</v>
+        <v>211.440429875</v>
       </c>
       <c r="P42">
-        <v>637.459185</v>
+        <v>634.321289625</v>
       </c>
       <c r="Q42">
-        <v>701.0591850000001</v>
+        <v>697.921289625</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08750476461028937</v>
+        <v>0.08809381495789234</v>
       </c>
       <c r="T42">
-        <v>0.8359161212791617</v>
+        <v>0.847722846155986</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.078716056618044</v>
+        <v>5.930454689383458</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06842660082515648</v>
+        <v>0.06830034288413933</v>
       </c>
       <c r="C43">
-        <v>6063.269858806867</v>
+        <v>6028.74635036395</v>
       </c>
       <c r="D43">
-        <v>7784.092858806867</v>
+        <v>7827.772350363949</v>
       </c>
       <c r="E43">
-        <v>3206.323</v>
+        <v>3284.526</v>
       </c>
       <c r="F43">
-        <v>3206.323</v>
+        <v>3284.526</v>
       </c>
       <c r="G43">
         <v>1485.5</v>
@@ -4819,28 +4819,28 @@
         <v>1017.3</v>
       </c>
       <c r="M43">
-        <v>171.5382805</v>
+        <v>175.722141</v>
       </c>
       <c r="N43">
-        <v>845.7617195</v>
+        <v>841.577859</v>
       </c>
       <c r="O43">
-        <v>211.440429875</v>
+        <v>210.39446475</v>
       </c>
       <c r="P43">
-        <v>634.321289625</v>
+        <v>631.18339425</v>
       </c>
       <c r="Q43">
-        <v>697.921289625</v>
+        <v>694.78339425</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08809381495789234</v>
+        <v>0.08870317738644712</v>
       </c>
       <c r="T43">
-        <v>0.847722846155986</v>
+        <v>0.8599366994768387</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.930454689383458</v>
+        <v>5.78925338725528</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06830034288413933</v>
+        <v>0.06817408494312219</v>
       </c>
       <c r="C44">
-        <v>6028.74635036395</v>
+        <v>5994.71581248789</v>
       </c>
       <c r="D44">
-        <v>7827.772350363949</v>
+        <v>7871.944812487889</v>
       </c>
       <c r="E44">
-        <v>3284.526</v>
+        <v>3362.729</v>
       </c>
       <c r="F44">
-        <v>3284.526</v>
+        <v>3362.729</v>
       </c>
       <c r="G44">
         <v>1485.5</v>
@@ -4901,28 +4901,28 @@
         <v>1017.3</v>
       </c>
       <c r="M44">
-        <v>175.722141</v>
+        <v>179.9060015</v>
       </c>
       <c r="N44">
-        <v>841.5778590000001</v>
+        <v>837.3939985000001</v>
       </c>
       <c r="O44">
-        <v>210.39446475</v>
+        <v>209.348499625</v>
       </c>
       <c r="P44">
-        <v>631.1833942500001</v>
+        <v>628.045498875</v>
       </c>
       <c r="Q44">
-        <v>694.7833942500001</v>
+        <v>691.645498875</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08870317738644712</v>
+        <v>0.08933392095284592</v>
       </c>
       <c r="T44">
-        <v>0.8599366994768387</v>
+        <v>0.8725791090545634</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.789253387255282</v>
+        <v>5.654619587551671</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06817408494312219</v>
+        <v>0.06831182700210503</v>
       </c>
       <c r="C45">
-        <v>5994.71581248789</v>
+        <v>5868.347113339169</v>
       </c>
       <c r="D45">
-        <v>7871.944812487889</v>
+        <v>7823.779113339169</v>
       </c>
       <c r="E45">
-        <v>3362.729</v>
+        <v>3440.932</v>
       </c>
       <c r="F45">
-        <v>3362.729</v>
+        <v>3440.932</v>
       </c>
       <c r="G45">
         <v>1485.5</v>
@@ -4983,45 +4983,45 @@
         <v>1017.3</v>
       </c>
       <c r="M45">
-        <v>179.9060015</v>
+        <v>186.8426076</v>
       </c>
       <c r="N45">
-        <v>837.3939985000001</v>
+        <v>830.4573924000001</v>
       </c>
       <c r="O45">
-        <v>209.348499625</v>
+        <v>207.6143481</v>
       </c>
       <c r="P45">
-        <v>628.045498875</v>
+        <v>622.8430443000001</v>
       </c>
       <c r="Q45">
-        <v>691.645498875</v>
+        <v>686.4430443000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08933392095284592</v>
+        <v>0.08998719107518754</v>
       </c>
       <c r="T45">
-        <v>0.8725791090545634</v>
+        <v>0.8856730332600642</v>
       </c>
       <c r="U45">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y45">
-        <v>5.654619587551671</v>
+        <v>5.444689586959073</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06831182700210503</v>
+        <v>0.06819156906108788</v>
       </c>
       <c r="C46">
-        <v>5868.347113339169</v>
+        <v>5832.163123466433</v>
       </c>
       <c r="D46">
-        <v>7823.779113339169</v>
+        <v>7865.798123466433</v>
       </c>
       <c r="E46">
-        <v>3440.932</v>
+        <v>3519.135</v>
       </c>
       <c r="F46">
-        <v>3440.932</v>
+        <v>3519.135</v>
       </c>
       <c r="G46">
         <v>1485.5</v>
@@ -5065,28 +5065,28 @@
         <v>1017.3</v>
       </c>
       <c r="M46">
-        <v>186.8426076</v>
+        <v>191.0890305</v>
       </c>
       <c r="N46">
-        <v>830.4573924000001</v>
+        <v>826.2109695</v>
       </c>
       <c r="O46">
-        <v>207.6143481</v>
+        <v>206.552742375</v>
       </c>
       <c r="P46">
-        <v>622.8430443000001</v>
+        <v>619.6582271250001</v>
       </c>
       <c r="Q46">
-        <v>686.4430443000001</v>
+        <v>683.2582271250001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08998719107518754</v>
+        <v>0.09066421647470524</v>
       </c>
       <c r="T46">
-        <v>0.8856730332600642</v>
+        <v>0.8992431001639466</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.444689586959073</v>
+        <v>5.323696485026648</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06819156906108788</v>
+        <v>0.06807131112007073</v>
       </c>
       <c r="C47">
-        <v>5832.163123466433</v>
+        <v>5796.432911964825</v>
       </c>
       <c r="D47">
-        <v>7865.798123466433</v>
+        <v>7908.270911964825</v>
       </c>
       <c r="E47">
-        <v>3519.135</v>
+        <v>3597.338</v>
       </c>
       <c r="F47">
-        <v>3519.135</v>
+        <v>3597.338</v>
       </c>
       <c r="G47">
         <v>1485.5</v>
@@ -5147,28 +5147,28 @@
         <v>1017.3</v>
       </c>
       <c r="M47">
-        <v>191.0890305</v>
+        <v>195.3354534</v>
       </c>
       <c r="N47">
-        <v>826.2109695</v>
+        <v>821.9645466000001</v>
       </c>
       <c r="O47">
-        <v>206.552742375</v>
+        <v>205.49113665</v>
       </c>
       <c r="P47">
-        <v>619.6582271250001</v>
+        <v>616.47340995</v>
       </c>
       <c r="Q47">
-        <v>683.2582271250001</v>
+        <v>680.07340995</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09066421647470524</v>
+        <v>0.09136631688901986</v>
       </c>
       <c r="T47">
-        <v>0.8992431001639466</v>
+        <v>0.9133157621383433</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.323696485026648</v>
+        <v>5.20796395274346</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06807131112007073</v>
+        <v>0.06795105317905357</v>
       </c>
       <c r="C48">
-        <v>5796.432911964825</v>
+        <v>5761.163869514891</v>
       </c>
       <c r="D48">
-        <v>7908.270911964825</v>
+        <v>7951.204869514891</v>
       </c>
       <c r="E48">
-        <v>3597.338</v>
+        <v>3675.541</v>
       </c>
       <c r="F48">
-        <v>3597.338</v>
+        <v>3675.541</v>
       </c>
       <c r="G48">
         <v>1485.5</v>
@@ -5229,28 +5229,28 @@
         <v>1017.3</v>
       </c>
       <c r="M48">
-        <v>195.3354534</v>
+        <v>199.5818763</v>
       </c>
       <c r="N48">
-        <v>821.9645466000001</v>
+        <v>817.7181237000001</v>
       </c>
       <c r="O48">
-        <v>205.49113665</v>
+        <v>204.429530925</v>
       </c>
       <c r="P48">
-        <v>616.47340995</v>
+        <v>613.2885927750001</v>
       </c>
       <c r="Q48">
-        <v>680.07340995</v>
+        <v>676.8885927750001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09136631688901986</v>
+        <v>0.09209491165859165</v>
       </c>
       <c r="T48">
-        <v>0.9133157621383433</v>
+        <v>0.9279194679608304</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.20796395274346</v>
+        <v>5.097156209068068</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06795105317905357</v>
+        <v>0.06783079523803644</v>
       </c>
       <c r="C49">
-        <v>5761.163869514891</v>
+        <v>5726.363548169104</v>
       </c>
       <c r="D49">
-        <v>7951.204869514891</v>
+        <v>7994.607548169105</v>
       </c>
       <c r="E49">
-        <v>3675.541</v>
+        <v>3753.744000000001</v>
       </c>
       <c r="F49">
-        <v>3675.541</v>
+        <v>3753.744000000001</v>
       </c>
       <c r="G49">
         <v>1485.5</v>
@@ -5311,28 +5311,28 @@
         <v>1017.3</v>
       </c>
       <c r="M49">
-        <v>199.5818763</v>
+        <v>203.8282992</v>
       </c>
       <c r="N49">
-        <v>817.7181237000001</v>
+        <v>813.4717008</v>
       </c>
       <c r="O49">
-        <v>204.429530925</v>
+        <v>203.3679252</v>
       </c>
       <c r="P49">
-        <v>613.2885927750001</v>
+        <v>610.1037756000001</v>
       </c>
       <c r="Q49">
-        <v>676.8885927750001</v>
+        <v>673.7037756000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09209491165859165</v>
+        <v>0.09285152930391621</v>
       </c>
       <c r="T49">
-        <v>0.9279194679608304</v>
+        <v>0.9430848547764901</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.097156209068068</v>
+        <v>4.990965454712482</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06783079523803644</v>
+        <v>0.06771053729701927</v>
       </c>
       <c r="C50">
-        <v>5726.363548169104</v>
+        <v>5692.039665780423</v>
       </c>
       <c r="D50">
-        <v>7994.607548169105</v>
+        <v>8038.486665780424</v>
       </c>
       <c r="E50">
-        <v>3753.744</v>
+        <v>3831.947</v>
       </c>
       <c r="F50">
-        <v>3753.744</v>
+        <v>3831.947</v>
       </c>
       <c r="G50">
         <v>1485.5</v>
@@ -5393,28 +5393,28 @@
         <v>1017.3</v>
       </c>
       <c r="M50">
-        <v>203.8282992</v>
+        <v>208.0747221</v>
       </c>
       <c r="N50">
-        <v>813.4717008</v>
+        <v>809.2252779</v>
       </c>
       <c r="O50">
-        <v>203.3679252</v>
+        <v>202.306319475</v>
       </c>
       <c r="P50">
-        <v>610.1037756000001</v>
+        <v>606.918958425</v>
       </c>
       <c r="Q50">
-        <v>673.7037756000001</v>
+        <v>670.5189584250001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09285152930391621</v>
+        <v>0.09363781822944957</v>
       </c>
       <c r="T50">
-        <v>0.9430848547764901</v>
+        <v>0.9588449626437442</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.990965454712483</v>
+        <v>4.889109016861208</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06771053729701927</v>
+        <v>0.06759027935600213</v>
       </c>
       <c r="C51">
-        <v>5692.039665780423</v>
+        <v>5658.200110577391</v>
       </c>
       <c r="D51">
-        <v>8038.486665780424</v>
+        <v>8082.850110577389</v>
       </c>
       <c r="E51">
-        <v>3831.947</v>
+        <v>3910.15</v>
       </c>
       <c r="F51">
-        <v>3831.947</v>
+        <v>3910.15</v>
       </c>
       <c r="G51">
         <v>1485.5</v>
@@ -5475,28 +5475,28 @@
         <v>1017.3</v>
       </c>
       <c r="M51">
-        <v>208.0747221</v>
+        <v>212.321145</v>
       </c>
       <c r="N51">
-        <v>809.2252779</v>
+        <v>804.9788550000001</v>
       </c>
       <c r="O51">
-        <v>202.306319475</v>
+        <v>201.24471375</v>
       </c>
       <c r="P51">
-        <v>606.918958425</v>
+        <v>603.73414125</v>
       </c>
       <c r="Q51">
-        <v>670.5189584250001</v>
+        <v>667.33414125</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09363781822944957</v>
+        <v>0.09445555871200427</v>
       </c>
       <c r="T51">
-        <v>0.9588449626437442</v>
+        <v>0.9752354748256886</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.889109016861208</v>
+        <v>4.791326836523984</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06759027935600213</v>
+        <v>0.06747002141498498</v>
       </c>
       <c r="C52">
-        <v>5658.200110577391</v>
+        <v>5624.852945891706</v>
       </c>
       <c r="D52">
-        <v>8082.850110577389</v>
+        <v>8127.705945891707</v>
       </c>
       <c r="E52">
-        <v>3910.15</v>
+        <v>3988.353</v>
       </c>
       <c r="F52">
-        <v>3910.15</v>
+        <v>3988.353</v>
       </c>
       <c r="G52">
         <v>1485.5</v>
@@ -5557,28 +5557,28 @@
         <v>1017.3</v>
       </c>
       <c r="M52">
-        <v>212.321145</v>
+        <v>216.5675679</v>
       </c>
       <c r="N52">
-        <v>804.9788550000001</v>
+        <v>800.7324321000001</v>
       </c>
       <c r="O52">
-        <v>201.24471375</v>
+        <v>200.183108025</v>
       </c>
       <c r="P52">
-        <v>603.73414125</v>
+        <v>600.5493240750001</v>
       </c>
       <c r="Q52">
-        <v>667.33414125</v>
+        <v>664.1493240750001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09445555871200427</v>
+        <v>0.09530667635711221</v>
       </c>
       <c r="T52">
-        <v>0.9752354748256886</v>
+        <v>0.9922949875048552</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.791326836523984</v>
+        <v>4.697379251494102</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06747002141498498</v>
+        <v>0.06734976347396783</v>
       </c>
       <c r="C53">
-        <v>5624.852945891706</v>
+        <v>5592.006415043979</v>
       </c>
       <c r="D53">
-        <v>8127.705945891707</v>
+        <v>8173.062415043981</v>
       </c>
       <c r="E53">
-        <v>3988.353</v>
+        <v>4066.556</v>
       </c>
       <c r="F53">
-        <v>3988.353</v>
+        <v>4066.556</v>
       </c>
       <c r="G53">
         <v>1485.5</v>
@@ -5639,28 +5639,28 @@
         <v>1017.3</v>
       </c>
       <c r="M53">
-        <v>216.5675679</v>
+        <v>220.8139908</v>
       </c>
       <c r="N53">
-        <v>800.7324321000001</v>
+        <v>796.4860092000001</v>
       </c>
       <c r="O53">
-        <v>200.183108025</v>
+        <v>199.1215023</v>
       </c>
       <c r="P53">
-        <v>600.5493240750001</v>
+        <v>597.3645069000002</v>
       </c>
       <c r="Q53">
-        <v>664.1493240750001</v>
+        <v>660.9645069000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09530667635711221</v>
+        <v>0.09619325723743299</v>
       </c>
       <c r="T53">
-        <v>0.9922949875048552</v>
+        <v>1.01006531321232</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.697379251494102</v>
+        <v>4.607045035119215</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06734976347396783</v>
+        <v>0.06722950553295068</v>
       </c>
       <c r="C54">
-        <v>5592.006415043979</v>
+        <v>5559.668946394042</v>
       </c>
       <c r="D54">
-        <v>8173.062415043981</v>
+        <v>8218.927946394042</v>
       </c>
       <c r="E54">
-        <v>4066.556</v>
+        <v>4144.759</v>
       </c>
       <c r="F54">
-        <v>4066.556</v>
+        <v>4144.759</v>
       </c>
       <c r="G54">
         <v>1485.5</v>
@@ -5721,28 +5721,28 @@
         <v>1017.3</v>
       </c>
       <c r="M54">
-        <v>220.8139908</v>
+        <v>225.0604137</v>
       </c>
       <c r="N54">
-        <v>796.4860092000001</v>
+        <v>792.2395863</v>
       </c>
       <c r="O54">
-        <v>199.1215023</v>
+        <v>198.059896575</v>
       </c>
       <c r="P54">
-        <v>597.3645069000002</v>
+        <v>594.179689725</v>
       </c>
       <c r="Q54">
-        <v>660.9645069000002</v>
+        <v>657.779689725</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09619325723743299</v>
+        <v>0.09711756496372487</v>
       </c>
       <c r="T54">
-        <v>1.01006531321232</v>
+        <v>1.028591822992444</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.607045035119215</v>
+        <v>4.520119657098098</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06722950553295068</v>
+        <v>0.06710924759193354</v>
       </c>
       <c r="C55">
-        <v>5559.668946394042</v>
+        <v>5527.849158562251</v>
       </c>
       <c r="D55">
-        <v>8218.927946394042</v>
+        <v>8265.311158562252</v>
       </c>
       <c r="E55">
-        <v>4144.759</v>
+        <v>4222.962</v>
       </c>
       <c r="F55">
-        <v>4144.759</v>
+        <v>4222.962</v>
       </c>
       <c r="G55">
         <v>1485.5</v>
@@ -5803,28 +5803,28 @@
         <v>1017.3</v>
       </c>
       <c r="M55">
-        <v>225.0604137</v>
+        <v>229.3068366</v>
       </c>
       <c r="N55">
-        <v>792.2395863</v>
+        <v>787.9931634000001</v>
       </c>
       <c r="O55">
-        <v>198.059896575</v>
+        <v>196.99829085</v>
       </c>
       <c r="P55">
-        <v>594.179689725</v>
+        <v>590.9948725500001</v>
       </c>
       <c r="Q55">
-        <v>657.779689725</v>
+        <v>654.5948725500001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09711756496372487</v>
+        <v>0.09808205998246422</v>
       </c>
       <c r="T55">
-        <v>1.028591822992444</v>
+        <v>1.04792383319779</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.520119657098098</v>
+        <v>4.436413737522207</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06710924759193354</v>
+        <v>0.06698898965091639</v>
       </c>
       <c r="C56">
-        <v>5527.849158562251</v>
+        <v>5496.555865828626</v>
       </c>
       <c r="D56">
-        <v>8265.311158562252</v>
+        <v>8312.220865828627</v>
       </c>
       <c r="E56">
-        <v>4222.962</v>
+        <v>4301.165000000001</v>
       </c>
       <c r="F56">
-        <v>4222.962</v>
+        <v>4301.165000000001</v>
       </c>
       <c r="G56">
         <v>1485.5</v>
@@ -5885,28 +5885,28 @@
         <v>1017.3</v>
       </c>
       <c r="M56">
-        <v>229.3068366</v>
+        <v>233.5532595000001</v>
       </c>
       <c r="N56">
-        <v>787.9931634000001</v>
+        <v>783.7467405</v>
       </c>
       <c r="O56">
-        <v>196.99829085</v>
+        <v>195.936685125</v>
       </c>
       <c r="P56">
-        <v>590.9948725500001</v>
+        <v>587.810055375</v>
       </c>
       <c r="Q56">
-        <v>654.5948725500001</v>
+        <v>651.4100553750001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09808205998246422</v>
+        <v>0.09908942144648086</v>
       </c>
       <c r="T56">
-        <v>1.04792383319779</v>
+        <v>1.068115043856707</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.436413737522207</v>
+        <v>4.355751669567256</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06698898965091639</v>
+        <v>0.06686873170989924</v>
       </c>
       <c r="C57">
-        <v>5496.555865828626</v>
+        <v>5465.798083716834</v>
       </c>
       <c r="D57">
-        <v>8312.220865828627</v>
+        <v>8359.666083716835</v>
       </c>
       <c r="E57">
-        <v>4301.165000000001</v>
+        <v>4379.368</v>
       </c>
       <c r="F57">
-        <v>4301.165000000001</v>
+        <v>4379.368</v>
       </c>
       <c r="G57">
         <v>1485.5</v>
@@ -5967,28 +5967,28 @@
         <v>1017.3</v>
       </c>
       <c r="M57">
-        <v>233.5532595000001</v>
+        <v>237.7996824</v>
       </c>
       <c r="N57">
-        <v>783.7467405</v>
+        <v>779.5003176</v>
       </c>
       <c r="O57">
-        <v>195.936685125</v>
+        <v>194.8750794</v>
       </c>
       <c r="P57">
-        <v>587.810055375</v>
+        <v>584.6252382</v>
       </c>
       <c r="Q57">
-        <v>651.4100553750001</v>
+        <v>648.2252382</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09908942144648086</v>
+        <v>0.1001425720679528</v>
       </c>
       <c r="T57">
-        <v>1.068115043856707</v>
+        <v>1.089224036818301</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.355751669567256</v>
+        <v>4.277970389753556</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06686873170989924</v>
+        <v>0.06717597376888208</v>
       </c>
       <c r="C58">
-        <v>5465.798083716834</v>
+        <v>5267.439574183546</v>
       </c>
       <c r="D58">
-        <v>8359.666083716835</v>
+        <v>8239.510574183547</v>
       </c>
       <c r="E58">
-        <v>4379.368</v>
+        <v>4457.571000000001</v>
       </c>
       <c r="F58">
-        <v>4379.368</v>
+        <v>4457.571000000001</v>
       </c>
       <c r="G58">
         <v>1485.5</v>
@@ -6049,45 +6049,45 @@
         <v>1017.3</v>
       </c>
       <c r="M58">
-        <v>237.7996824</v>
+        <v>246.5036763000001</v>
       </c>
       <c r="N58">
-        <v>779.5003176</v>
+        <v>770.7963237</v>
       </c>
       <c r="O58">
-        <v>194.8750794</v>
+        <v>192.699080925</v>
       </c>
       <c r="P58">
-        <v>584.6252382</v>
+        <v>578.097242775</v>
       </c>
       <c r="Q58">
-        <v>648.2252382</v>
+        <v>641.6972427750001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1001425720679528</v>
+        <v>0.1012447064392607</v>
       </c>
       <c r="T58">
-        <v>1.089224036818301</v>
+        <v>1.111314843406017</v>
       </c>
       <c r="U58">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>4.277970389753556</v>
+        <v>4.126916138816222</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06717597376888208</v>
+        <v>0.06706321582786494</v>
       </c>
       <c r="C59">
-        <v>5267.439574183546</v>
+        <v>5232.930352907103</v>
       </c>
       <c r="D59">
-        <v>8239.510574183547</v>
+        <v>8283.204352907103</v>
       </c>
       <c r="E59">
-        <v>4457.571000000001</v>
+        <v>4535.774</v>
       </c>
       <c r="F59">
-        <v>4457.571000000001</v>
+        <v>4535.774</v>
       </c>
       <c r="G59">
         <v>1485.5</v>
@@ -6131,28 +6131,28 @@
         <v>1017.3</v>
       </c>
       <c r="M59">
-        <v>246.5036763000001</v>
+        <v>250.8283022</v>
       </c>
       <c r="N59">
-        <v>770.7963237</v>
+        <v>766.4716978</v>
       </c>
       <c r="O59">
-        <v>192.699080925</v>
+        <v>191.61792445</v>
       </c>
       <c r="P59">
-        <v>578.097242775</v>
+        <v>574.85377335</v>
       </c>
       <c r="Q59">
-        <v>641.6972427750001</v>
+        <v>638.45377335</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1012447064392607</v>
+        <v>0.1023993233996784</v>
       </c>
       <c r="T59">
-        <v>1.111314843406017</v>
+        <v>1.134457593164577</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.126916138816222</v>
+        <v>4.055762412284908</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06706321582786494</v>
+        <v>0.06695045788684779</v>
       </c>
       <c r="C60">
-        <v>5232.930352907104</v>
+        <v>5198.887014738296</v>
       </c>
       <c r="D60">
-        <v>8283.204352907103</v>
+        <v>8327.364014738296</v>
       </c>
       <c r="E60">
-        <v>4535.773999999999</v>
+        <v>4613.977</v>
       </c>
       <c r="F60">
-        <v>4535.773999999999</v>
+        <v>4613.977</v>
       </c>
       <c r="G60">
         <v>1485.5</v>
@@ -6213,28 +6213,28 @@
         <v>1017.3</v>
       </c>
       <c r="M60">
-        <v>250.8283022</v>
+        <v>255.1529281</v>
       </c>
       <c r="N60">
-        <v>766.4716978000001</v>
+        <v>762.1470719000001</v>
       </c>
       <c r="O60">
-        <v>191.61792445</v>
+        <v>190.536767975</v>
       </c>
       <c r="P60">
-        <v>574.8537733500001</v>
+        <v>571.6103039250002</v>
       </c>
       <c r="Q60">
-        <v>638.4537733500001</v>
+        <v>635.2103039250002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1023993233996784</v>
+        <v>0.1036102631386532</v>
       </c>
       <c r="T60">
-        <v>1.134457593164576</v>
+        <v>1.158729257545504</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.05576241228491</v>
+        <v>3.98702067648347</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06695045788684779</v>
+        <v>0.06683769994583064</v>
       </c>
       <c r="C61">
-        <v>5198.887014738296</v>
+        <v>5165.317050803074</v>
       </c>
       <c r="D61">
-        <v>8327.364014738296</v>
+        <v>8371.997050803075</v>
       </c>
       <c r="E61">
-        <v>4613.977</v>
+        <v>4692.18</v>
       </c>
       <c r="F61">
-        <v>4613.977</v>
+        <v>4692.18</v>
       </c>
       <c r="G61">
         <v>1485.5</v>
@@ -6295,28 +6295,28 @@
         <v>1017.3</v>
       </c>
       <c r="M61">
-        <v>255.1529281</v>
+        <v>259.477554</v>
       </c>
       <c r="N61">
-        <v>762.1470719000001</v>
+        <v>757.8224460000001</v>
       </c>
       <c r="O61">
-        <v>190.536767975</v>
+        <v>189.4556115</v>
       </c>
       <c r="P61">
-        <v>571.6103039250002</v>
+        <v>568.3668345000001</v>
       </c>
       <c r="Q61">
-        <v>635.2103039250002</v>
+        <v>631.9668345000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1036102631386532</v>
+        <v>0.1048817498645766</v>
       </c>
       <c r="T61">
-        <v>1.158729257545504</v>
+        <v>1.184214505145479</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.98702067648347</v>
+        <v>3.920570331875412</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06683769994583064</v>
+        <v>0.06672494200481349</v>
       </c>
       <c r="C62">
-        <v>5165.317050803074</v>
+        <v>5132.228113696678</v>
       </c>
       <c r="D62">
-        <v>8371.997050803075</v>
+        <v>8417.111113696677</v>
       </c>
       <c r="E62">
-        <v>4692.18</v>
+        <v>4770.383</v>
       </c>
       <c r="F62">
-        <v>4692.18</v>
+        <v>4770.383</v>
       </c>
       <c r="G62">
         <v>1485.5</v>
@@ -6377,28 +6377,28 @@
         <v>1017.3</v>
       </c>
       <c r="M62">
-        <v>259.477554</v>
+        <v>263.8021799</v>
       </c>
       <c r="N62">
-        <v>757.8224460000001</v>
+        <v>753.4978201000001</v>
       </c>
       <c r="O62">
-        <v>189.4556115</v>
+        <v>188.374455025</v>
       </c>
       <c r="P62">
-        <v>568.3668345000001</v>
+        <v>565.123365075</v>
       </c>
       <c r="Q62">
-        <v>631.9668345000001</v>
+        <v>628.7233650750001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1048817498645766</v>
+        <v>0.1062184410379833</v>
       </c>
       <c r="T62">
-        <v>1.184214505145479</v>
+        <v>1.211006688519811</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.920570331875412</v>
+        <v>3.856298687090569</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06672494200481349</v>
+        <v>0.06661218406379635</v>
       </c>
       <c r="C63">
-        <v>5132.228113696678</v>
+        <v>5099.628021857764</v>
       </c>
       <c r="D63">
-        <v>8417.111113696677</v>
+        <v>8462.714021857764</v>
       </c>
       <c r="E63">
-        <v>4770.383</v>
+        <v>4848.586</v>
       </c>
       <c r="F63">
-        <v>4770.383</v>
+        <v>4848.586</v>
       </c>
       <c r="G63">
         <v>1485.5</v>
@@ -6459,28 +6459,28 @@
         <v>1017.3</v>
       </c>
       <c r="M63">
-        <v>263.8021799</v>
+        <v>268.1268058</v>
       </c>
       <c r="N63">
-        <v>753.4978201000001</v>
+        <v>749.1731942000001</v>
       </c>
       <c r="O63">
-        <v>188.374455025</v>
+        <v>187.29329855</v>
       </c>
       <c r="P63">
-        <v>565.123365075</v>
+        <v>561.8798956500001</v>
       </c>
       <c r="Q63">
-        <v>628.7233650750001</v>
+        <v>625.4798956500001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1062184410379833</v>
+        <v>0.1076254843784114</v>
       </c>
       <c r="T63">
-        <v>1.211006688519811</v>
+        <v>1.239208986808582</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.856298687090569</v>
+        <v>3.794100321169754</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06661218406379635</v>
+        <v>0.0664994261227792</v>
       </c>
       <c r="C64">
-        <v>5099.628021857764</v>
+        <v>5067.524764085473</v>
       </c>
       <c r="D64">
-        <v>8462.714021857764</v>
+        <v>8508.813764085473</v>
       </c>
       <c r="E64">
-        <v>4848.586</v>
+        <v>4926.789</v>
       </c>
       <c r="F64">
-        <v>4848.586</v>
+        <v>4926.789</v>
       </c>
       <c r="G64">
         <v>1485.5</v>
@@ -6541,28 +6541,28 @@
         <v>1017.3</v>
       </c>
       <c r="M64">
-        <v>268.1268058</v>
+        <v>272.4514317</v>
       </c>
       <c r="N64">
-        <v>749.1731942000001</v>
+        <v>744.8485683000001</v>
       </c>
       <c r="O64">
-        <v>187.29329855</v>
+        <v>186.212142075</v>
       </c>
       <c r="P64">
-        <v>561.8798956500001</v>
+        <v>558.6364262250002</v>
       </c>
       <c r="Q64">
-        <v>625.4798956500001</v>
+        <v>622.2364262250002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1076254843784114</v>
+        <v>0.1091085841156195</v>
       </c>
       <c r="T64">
-        <v>1.239208986808582</v>
+        <v>1.268935733653502</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.794100321169754</v>
+        <v>3.733876506548012</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0664994261227792</v>
+        <v>0.06638666818176205</v>
       </c>
       <c r="C65">
-        <v>5067.524764085473</v>
+        <v>5035.926504204939</v>
       </c>
       <c r="D65">
-        <v>8508.813764085473</v>
+        <v>8555.418504204939</v>
       </c>
       <c r="E65">
-        <v>4926.789</v>
+        <v>5004.992</v>
       </c>
       <c r="F65">
-        <v>4926.789</v>
+        <v>5004.992</v>
       </c>
       <c r="G65">
         <v>1485.5</v>
@@ -6623,28 +6623,28 @@
         <v>1017.3</v>
       </c>
       <c r="M65">
-        <v>272.4514317</v>
+        <v>276.7760576</v>
       </c>
       <c r="N65">
-        <v>744.8485683000001</v>
+        <v>740.5239424000001</v>
       </c>
       <c r="O65">
-        <v>186.212142075</v>
+        <v>185.1309856</v>
       </c>
       <c r="P65">
-        <v>558.6364262250002</v>
+        <v>555.3929568000001</v>
       </c>
       <c r="Q65">
-        <v>622.2364262250002</v>
+        <v>618.9929568000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1091085841156195</v>
+        <v>0.1106740782826724</v>
       </c>
       <c r="T65">
-        <v>1.268935733653502</v>
+        <v>1.300313966434252</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.733876506548012</v>
+        <v>3.675534686133199</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.06638666818176205</v>
+        <v>0.0662739102407449</v>
       </c>
       <c r="C66">
-        <v>5035.926504204939</v>
+        <v>5004.841585886977</v>
       </c>
       <c r="D66">
-        <v>8555.418504204939</v>
+        <v>8602.536585886977</v>
       </c>
       <c r="E66">
-        <v>5004.992</v>
+        <v>5083.195000000001</v>
       </c>
       <c r="F66">
-        <v>5004.992</v>
+        <v>5083.195000000001</v>
       </c>
       <c r="G66">
         <v>1485.5</v>
@@ -6705,28 +6705,28 @@
         <v>1017.3</v>
       </c>
       <c r="M66">
-        <v>276.7760576</v>
+        <v>281.1006835000001</v>
       </c>
       <c r="N66">
-        <v>740.5239424000001</v>
+        <v>736.1993165</v>
       </c>
       <c r="O66">
-        <v>185.1309856</v>
+        <v>184.049829125</v>
       </c>
       <c r="P66">
-        <v>555.3929568000001</v>
+        <v>552.149487375</v>
       </c>
       <c r="Q66">
-        <v>618.9929568000001</v>
+        <v>615.7494873750001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1106740782826724</v>
+        <v>0.1123290292592712</v>
       </c>
       <c r="T66">
-        <v>1.300313966434252</v>
+        <v>1.333485241088187</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.675534686133199</v>
+        <v>3.618987998654225</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0662739102407449</v>
+        <v>0.06616115229972774</v>
       </c>
       <c r="C67">
-        <v>5004.841585886977</v>
+        <v>4974.278537627938</v>
       </c>
       <c r="D67">
-        <v>8602.536585886977</v>
+        <v>8650.176537627938</v>
       </c>
       <c r="E67">
-        <v>5083.195000000001</v>
+        <v>5161.398</v>
       </c>
       <c r="F67">
-        <v>5083.195000000001</v>
+        <v>5161.398</v>
       </c>
       <c r="G67">
         <v>1485.5</v>
@@ -6787,28 +6787,28 @@
         <v>1017.3</v>
       </c>
       <c r="M67">
-        <v>281.1006835000001</v>
+        <v>285.4253094</v>
       </c>
       <c r="N67">
-        <v>736.1993165</v>
+        <v>731.8746906000001</v>
       </c>
       <c r="O67">
-        <v>184.049829125</v>
+        <v>182.96867265</v>
       </c>
       <c r="P67">
-        <v>552.149487375</v>
+        <v>548.9060179500001</v>
       </c>
       <c r="Q67">
-        <v>615.7494873750001</v>
+        <v>612.5060179500001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1123290292592712</v>
+        <v>0.1140813302933169</v>
       </c>
       <c r="T67">
-        <v>1.333485241088187</v>
+        <v>1.368607767192353</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.618987998654225</v>
+        <v>3.564154847159466</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.06616115229972774</v>
+        <v>0.0660483943587106</v>
       </c>
       <c r="C68">
-        <v>4974.278537627938</v>
+        <v>4944.246077895896</v>
       </c>
       <c r="D68">
-        <v>8650.176537627938</v>
+        <v>8698.347077895896</v>
       </c>
       <c r="E68">
-        <v>5161.398</v>
+        <v>5239.601000000001</v>
       </c>
       <c r="F68">
-        <v>5161.398</v>
+        <v>5239.601000000001</v>
       </c>
       <c r="G68">
         <v>1485.5</v>
@@ -6869,28 +6869,28 @@
         <v>1017.3</v>
       </c>
       <c r="M68">
-        <v>285.4253094</v>
+        <v>289.7499353000001</v>
       </c>
       <c r="N68">
-        <v>731.8746906000001</v>
+        <v>727.5500647</v>
       </c>
       <c r="O68">
-        <v>182.96867265</v>
+        <v>181.887516175</v>
       </c>
       <c r="P68">
-        <v>548.9060179500001</v>
+        <v>545.662548525</v>
       </c>
       <c r="Q68">
-        <v>612.5060179500001</v>
+        <v>609.2625485250001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1140813302933169</v>
+        <v>0.1159398313900321</v>
       </c>
       <c r="T68">
-        <v>1.368607767192353</v>
+        <v>1.405858931242226</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.564154847159466</v>
+        <v>3.510958506157084</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0660483943587106</v>
+        <v>0.06593563641769346</v>
       </c>
       <c r="C69">
-        <v>4944.246077895896</v>
+        <v>4914.753120449812</v>
       </c>
       <c r="D69">
-        <v>8698.347077895896</v>
+        <v>8747.057120449812</v>
       </c>
       <c r="E69">
-        <v>5239.601000000001</v>
+        <v>5317.804</v>
       </c>
       <c r="F69">
-        <v>5239.601000000001</v>
+        <v>5317.804</v>
       </c>
       <c r="G69">
         <v>1485.5</v>
@@ -6951,28 +6951,28 @@
         <v>1017.3</v>
       </c>
       <c r="M69">
-        <v>289.7499353000001</v>
+        <v>294.0745612</v>
       </c>
       <c r="N69">
-        <v>727.5500647</v>
+        <v>723.2254388000001</v>
       </c>
       <c r="O69">
-        <v>181.887516175</v>
+        <v>180.8063597</v>
       </c>
       <c r="P69">
-        <v>545.662548525</v>
+        <v>542.4190791000001</v>
       </c>
       <c r="Q69">
-        <v>609.2625485250001</v>
+        <v>606.0190791000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1159398313900321</v>
+        <v>0.117914488805292</v>
       </c>
       <c r="T69">
-        <v>1.405858931242226</v>
+        <v>1.445438293045217</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.510958506157084</v>
+        <v>3.459326763419481</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.06593563641769346</v>
+        <v>0.0658228784766763</v>
       </c>
       <c r="C70">
-        <v>4914.753120449812</v>
+        <v>4885.808779838385</v>
       </c>
       <c r="D70">
-        <v>8747.057120449812</v>
+        <v>8796.315779838385</v>
       </c>
       <c r="E70">
-        <v>5317.804</v>
+        <v>5396.007000000001</v>
       </c>
       <c r="F70">
-        <v>5317.804</v>
+        <v>5396.007000000001</v>
       </c>
       <c r="G70">
         <v>1485.5</v>
@@ -7033,28 +7033,28 @@
         <v>1017.3</v>
       </c>
       <c r="M70">
-        <v>294.0745612</v>
+        <v>298.3991871000001</v>
       </c>
       <c r="N70">
-        <v>723.2254388000001</v>
+        <v>718.9008129</v>
       </c>
       <c r="O70">
-        <v>180.8063597</v>
+        <v>179.725203225</v>
       </c>
       <c r="P70">
-        <v>542.4190791000001</v>
+        <v>539.175609675</v>
       </c>
       <c r="Q70">
-        <v>606.0190791000001</v>
+        <v>602.7756096750001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.117914488805292</v>
+        <v>0.1200165434731494</v>
       </c>
       <c r="T70">
-        <v>1.445438293045217</v>
+        <v>1.487571162061304</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.459326763419481</v>
+        <v>3.40919159293514</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0658228784766763</v>
+        <v>0.06571012053565914</v>
       </c>
       <c r="C71">
-        <v>4885.808779838385</v>
+        <v>4857.422377085744</v>
       </c>
       <c r="D71">
-        <v>8796.315779838385</v>
+        <v>8846.132377085745</v>
       </c>
       <c r="E71">
-        <v>5396.007000000001</v>
+        <v>5474.210000000001</v>
       </c>
       <c r="F71">
-        <v>5396.007000000001</v>
+        <v>5474.210000000001</v>
       </c>
       <c r="G71">
         <v>1485.5</v>
@@ -7115,28 +7115,28 @@
         <v>1017.3</v>
       </c>
       <c r="M71">
-        <v>298.3991871000001</v>
+        <v>302.7238130000001</v>
       </c>
       <c r="N71">
-        <v>718.9008129</v>
+        <v>714.576187</v>
       </c>
       <c r="O71">
-        <v>179.725203225</v>
+        <v>178.64404675</v>
       </c>
       <c r="P71">
-        <v>539.175609675</v>
+        <v>535.93214025</v>
       </c>
       <c r="Q71">
-        <v>602.7756096750001</v>
+        <v>599.53214025</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1200165434731494</v>
+        <v>0.1222587351188638</v>
       </c>
       <c r="T71">
-        <v>1.487571162061304</v>
+        <v>1.532512889011796</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.40919159293514</v>
+        <v>3.360488855893209</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.06571012053565914</v>
+        <v>0.06559736259464201</v>
       </c>
       <c r="C72">
-        <v>4857.422377085744</v>
+        <v>4829.603445571469</v>
       </c>
       <c r="D72">
-        <v>8846.132377085745</v>
+        <v>8896.516445571469</v>
       </c>
       <c r="E72">
-        <v>5474.210000000001</v>
+        <v>5552.413</v>
       </c>
       <c r="F72">
-        <v>5474.210000000001</v>
+        <v>5552.413</v>
       </c>
       <c r="G72">
         <v>1485.5</v>
@@ -7197,28 +7197,28 @@
         <v>1017.3</v>
       </c>
       <c r="M72">
-        <v>302.7238130000001</v>
+        <v>307.0484389000001</v>
       </c>
       <c r="N72">
-        <v>714.576187</v>
+        <v>710.2515611</v>
       </c>
       <c r="O72">
-        <v>178.64404675</v>
+        <v>177.562890275</v>
       </c>
       <c r="P72">
-        <v>535.93214025</v>
+        <v>532.688670825</v>
       </c>
       <c r="Q72">
-        <v>599.53214025</v>
+        <v>596.2886708250001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1222587351188638</v>
+        <v>0.1246555606711794</v>
       </c>
       <c r="T72">
-        <v>1.532512889011796</v>
+        <v>1.580554045407151</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.360488855893209</v>
+        <v>3.313158026936967</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.06559736259464201</v>
+        <v>0.06548460465362485</v>
       </c>
       <c r="C73">
-        <v>4829.60344557147</v>
+        <v>4802.361737112735</v>
       </c>
       <c r="D73">
-        <v>8896.516445571469</v>
+        <v>8947.477737112735</v>
       </c>
       <c r="E73">
-        <v>5552.413</v>
+        <v>5630.616</v>
       </c>
       <c r="F73">
-        <v>5552.413</v>
+        <v>5630.616</v>
       </c>
       <c r="G73">
         <v>1485.5</v>
@@ -7279,28 +7279,28 @@
         <v>1017.3</v>
       </c>
       <c r="M73">
-        <v>307.0484389</v>
+        <v>311.3730648</v>
       </c>
       <c r="N73">
-        <v>710.2515611000001</v>
+        <v>705.9269352000001</v>
       </c>
       <c r="O73">
-        <v>177.562890275</v>
+        <v>176.4817338</v>
       </c>
       <c r="P73">
-        <v>532.6886708250001</v>
+        <v>529.4452014000001</v>
       </c>
       <c r="Q73">
-        <v>596.2886708250002</v>
+        <v>593.0452014000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1246555606711793</v>
+        <v>0.1272235880486602</v>
       </c>
       <c r="T73">
-        <v>1.58055404540715</v>
+        <v>1.632026712973601</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.313158026936968</v>
+        <v>3.26714194322951</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.06548460465362485</v>
+        <v>0.06537184671260771</v>
       </c>
       <c r="C74">
-        <v>4802.361737112735</v>
+        <v>4775.70722825658</v>
       </c>
       <c r="D74">
-        <v>8947.477737112735</v>
+        <v>8999.02622825658</v>
       </c>
       <c r="E74">
-        <v>5630.616</v>
+        <v>5708.819</v>
       </c>
       <c r="F74">
-        <v>5630.616</v>
+        <v>5708.819</v>
       </c>
       <c r="G74">
         <v>1485.5</v>
@@ -7361,28 +7361,28 @@
         <v>1017.3</v>
       </c>
       <c r="M74">
-        <v>311.3730648</v>
+        <v>315.6976907</v>
       </c>
       <c r="N74">
-        <v>705.9269352000001</v>
+        <v>701.6023093000001</v>
       </c>
       <c r="O74">
-        <v>176.4817338</v>
+        <v>175.400577325</v>
       </c>
       <c r="P74">
-        <v>529.4452014000001</v>
+        <v>526.201731975</v>
       </c>
       <c r="Q74">
-        <v>593.0452014000001</v>
+        <v>589.8017319750001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1272235880486602</v>
+        <v>0.1299818396763248</v>
       </c>
       <c r="T74">
-        <v>1.632026712973601</v>
+        <v>1.687312170730159</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.26714194322951</v>
+        <v>3.222386574144174</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.06537184671260771</v>
+        <v>0.06525908877159056</v>
       </c>
       <c r="C75">
-        <v>4775.70722825658</v>
+        <v>4749.650126791096</v>
       </c>
       <c r="D75">
-        <v>8999.02622825658</v>
+        <v>9051.172126791096</v>
       </c>
       <c r="E75">
-        <v>5708.819</v>
+        <v>5787.022</v>
       </c>
       <c r="F75">
-        <v>5708.819</v>
+        <v>5787.022</v>
       </c>
       <c r="G75">
         <v>1485.5</v>
@@ -7443,28 +7443,28 @@
         <v>1017.3</v>
       </c>
       <c r="M75">
-        <v>315.6976907</v>
+        <v>320.0223166</v>
       </c>
       <c r="N75">
-        <v>701.6023093000001</v>
+        <v>697.2776834000001</v>
       </c>
       <c r="O75">
-        <v>175.400577325</v>
+        <v>174.31942085</v>
       </c>
       <c r="P75">
-        <v>526.201731975</v>
+        <v>522.9582625500001</v>
       </c>
       <c r="Q75">
-        <v>589.8017319750001</v>
+        <v>586.5582625500001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1299818396763248</v>
+        <v>0.1329522645061175</v>
       </c>
       <c r="T75">
-        <v>1.687312170730159</v>
+        <v>1.746850356006453</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.222386574144174</v>
+        <v>3.178840809628712</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.06525908877159056</v>
+        <v>0.0651463308305734</v>
       </c>
       <c r="C76">
-        <v>4749.650126791096</v>
+        <v>4724.200878484207</v>
       </c>
       <c r="D76">
-        <v>9051.172126791096</v>
+        <v>9103.925878484208</v>
       </c>
       <c r="E76">
-        <v>5787.022</v>
+        <v>5865.225</v>
       </c>
       <c r="F76">
-        <v>5787.022</v>
+        <v>5865.225</v>
       </c>
       <c r="G76">
         <v>1485.5</v>
@@ -7525,28 +7525,28 @@
         <v>1017.3</v>
       </c>
       <c r="M76">
-        <v>320.0223166</v>
+        <v>324.3469425</v>
       </c>
       <c r="N76">
-        <v>697.2776834000001</v>
+        <v>692.9530575000001</v>
       </c>
       <c r="O76">
-        <v>174.31942085</v>
+        <v>173.238264375</v>
       </c>
       <c r="P76">
-        <v>522.9582625500001</v>
+        <v>519.7147931250001</v>
       </c>
       <c r="Q76">
-        <v>586.5582625500001</v>
+        <v>583.3147931250002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1329522645061175</v>
+        <v>0.1361603233222936</v>
       </c>
       <c r="T76">
-        <v>1.746850356006453</v>
+        <v>1.81115159610485</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.178840809628712</v>
+        <v>3.13645626550033</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0651463308305734</v>
+        <v>0.06503357288955626</v>
       </c>
       <c r="C77">
-        <v>4724.200878484207</v>
+        <v>4699.370174059513</v>
       </c>
       <c r="D77">
-        <v>9103.925878484208</v>
+        <v>9157.298174059513</v>
       </c>
       <c r="E77">
-        <v>5865.225</v>
+        <v>5943.428</v>
       </c>
       <c r="F77">
-        <v>5865.225</v>
+        <v>5943.428</v>
       </c>
       <c r="G77">
         <v>1485.5</v>
@@ -7607,28 +7607,28 @@
         <v>1017.3</v>
       </c>
       <c r="M77">
-        <v>324.3469425</v>
+        <v>328.6715684</v>
       </c>
       <c r="N77">
-        <v>692.9530575000001</v>
+        <v>688.6284316000001</v>
       </c>
       <c r="O77">
-        <v>173.238264375</v>
+        <v>172.1571079</v>
       </c>
       <c r="P77">
-        <v>519.7147931250001</v>
+        <v>516.4713237000001</v>
       </c>
       <c r="Q77">
-        <v>583.3147931250002</v>
+        <v>580.0713237000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1361603233222936</v>
+        <v>0.1396357203731511</v>
       </c>
       <c r="T77">
-        <v>1.81115159610485</v>
+        <v>1.880811272878114</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.13645626550033</v>
+        <v>3.095187104112167</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.06503357288955626</v>
+        <v>0.0649208149485391</v>
       </c>
       <c r="C78">
-        <v>4699.370174059513</v>
+        <v>4675.168956419005</v>
       </c>
       <c r="D78">
-        <v>9157.298174059513</v>
+        <v>9211.299956419005</v>
       </c>
       <c r="E78">
-        <v>5943.428</v>
+        <v>6021.631</v>
       </c>
       <c r="F78">
-        <v>5943.428</v>
+        <v>6021.631</v>
       </c>
       <c r="G78">
         <v>1485.5</v>
@@ -7689,28 +7689,28 @@
         <v>1017.3</v>
       </c>
       <c r="M78">
-        <v>328.6715684</v>
+        <v>332.9961943</v>
       </c>
       <c r="N78">
-        <v>688.6284316000001</v>
+        <v>684.3038057000001</v>
       </c>
       <c r="O78">
-        <v>172.1571079</v>
+        <v>171.075951425</v>
       </c>
       <c r="P78">
-        <v>516.4713237000001</v>
+        <v>513.227854275</v>
       </c>
       <c r="Q78">
-        <v>580.0713237000001</v>
+        <v>576.827854275</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1396357203731511</v>
+        <v>0.1434133258632135</v>
       </c>
       <c r="T78">
-        <v>1.880811272878114</v>
+        <v>1.956528312849052</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.095187104112167</v>
+        <v>3.054989868993828</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0649208149485391</v>
+        <v>0.06480805700752196</v>
       </c>
       <c r="C79">
-        <v>4675.168956419005</v>
+        <v>4651.60842812277</v>
       </c>
       <c r="D79">
-        <v>9211.299956419005</v>
+        <v>9265.942428122771</v>
       </c>
       <c r="E79">
-        <v>6021.631</v>
+        <v>6099.834000000001</v>
       </c>
       <c r="F79">
-        <v>6021.631</v>
+        <v>6099.834000000001</v>
       </c>
       <c r="G79">
         <v>1485.5</v>
@@ -7771,28 +7771,28 @@
         <v>1017.3</v>
       </c>
       <c r="M79">
-        <v>332.9961943</v>
+        <v>337.3208202000001</v>
       </c>
       <c r="N79">
-        <v>684.3038057000001</v>
+        <v>679.9791798</v>
       </c>
       <c r="O79">
-        <v>171.075951425</v>
+        <v>169.99479495</v>
       </c>
       <c r="P79">
-        <v>513.227854275</v>
+        <v>509.98438485</v>
       </c>
       <c r="Q79">
-        <v>576.827854275</v>
+        <v>573.58438485</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1434133258632135</v>
+        <v>0.1475343500341907</v>
       </c>
       <c r="T79">
-        <v>1.956528312849052</v>
+        <v>2.039128720090076</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.054989868993828</v>
+        <v>3.015823332211855</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.06480805700752196</v>
+        <v>0.0661765490665048</v>
       </c>
       <c r="C80">
-        <v>4651.60842812277</v>
+        <v>3951.103359676727</v>
       </c>
       <c r="D80">
-        <v>9265.942428122771</v>
+        <v>8643.640359676727</v>
       </c>
       <c r="E80">
-        <v>6099.834000000001</v>
+        <v>6178.037</v>
       </c>
       <c r="F80">
-        <v>6099.834000000001</v>
+        <v>6178.037</v>
       </c>
       <c r="G80">
         <v>1485.5</v>
@@ -7853,45 +7853,45 @@
         <v>1017.3</v>
       </c>
       <c r="M80">
-        <v>337.3208202000001</v>
+        <v>357.0905386000001</v>
       </c>
       <c r="N80">
-        <v>679.9791798</v>
+        <v>660.2094614</v>
       </c>
       <c r="O80">
-        <v>169.99479495</v>
+        <v>165.05236535</v>
       </c>
       <c r="P80">
-        <v>509.98438485</v>
+        <v>495.15709605</v>
       </c>
       <c r="Q80">
-        <v>573.58438485</v>
+        <v>558.75709605</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1475343500341907</v>
+        <v>0.152047852697642</v>
       </c>
       <c r="T80">
-        <v>2.039128720090076</v>
+        <v>2.129595832782627</v>
       </c>
       <c r="U80">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V80">
         <v>0.25</v>
       </c>
       <c r="W80">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y80">
-        <v>3.015823332211855</v>
+        <v>2.848857334580749</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0661765490665048</v>
+        <v>0.06608254112548767</v>
       </c>
       <c r="C81">
-        <v>3951.103359676727</v>
+        <v>3912.962935074872</v>
       </c>
       <c r="D81">
-        <v>8643.640359676727</v>
+        <v>8683.702935074873</v>
       </c>
       <c r="E81">
-        <v>6178.037</v>
+        <v>6256.240000000001</v>
       </c>
       <c r="F81">
-        <v>6178.037</v>
+        <v>6256.240000000001</v>
       </c>
       <c r="G81">
         <v>1485.5</v>
@@ -7935,28 +7935,28 @@
         <v>1017.3</v>
       </c>
       <c r="M81">
-        <v>357.0905386000001</v>
+        <v>361.6106720000001</v>
       </c>
       <c r="N81">
-        <v>660.2094614</v>
+        <v>655.6893279999999</v>
       </c>
       <c r="O81">
-        <v>165.05236535</v>
+        <v>163.922332</v>
       </c>
       <c r="P81">
-        <v>495.15709605</v>
+        <v>491.7669959999999</v>
       </c>
       <c r="Q81">
-        <v>558.75709605</v>
+        <v>555.366996</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.152047852697642</v>
+        <v>0.1570127056274384</v>
       </c>
       <c r="T81">
-        <v>2.129595832782627</v>
+        <v>2.229109656744432</v>
       </c>
       <c r="U81">
         <v>0.0578</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.848857334580749</v>
+        <v>2.813246617898489</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.06608254112548767</v>
+        <v>0.06598853318447051</v>
       </c>
       <c r="C82">
-        <v>3912.962935074872</v>
+        <v>3875.195613381556</v>
       </c>
       <c r="D82">
-        <v>8683.702935074873</v>
+        <v>8724.138613381556</v>
       </c>
       <c r="E82">
-        <v>6256.240000000001</v>
+        <v>6334.443</v>
       </c>
       <c r="F82">
-        <v>6256.240000000001</v>
+        <v>6334.443</v>
       </c>
       <c r="G82">
         <v>1485.5</v>
@@ -8017,28 +8017,28 @@
         <v>1017.3</v>
       </c>
       <c r="M82">
-        <v>361.6106720000001</v>
+        <v>366.1308054</v>
       </c>
       <c r="N82">
-        <v>655.6893279999999</v>
+        <v>651.1691946000001</v>
       </c>
       <c r="O82">
-        <v>163.922332</v>
+        <v>162.79229865</v>
       </c>
       <c r="P82">
-        <v>491.7669959999999</v>
+        <v>488.3768959500001</v>
       </c>
       <c r="Q82">
-        <v>555.366996</v>
+        <v>551.9768959500001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1570127056274384</v>
+        <v>0.162500174655108</v>
       </c>
       <c r="T82">
-        <v>2.229109656744432</v>
+        <v>2.339098620070637</v>
       </c>
       <c r="U82">
         <v>0.0578</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.813246617898489</v>
+        <v>2.778515178171348</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.06598853318447051</v>
+        <v>0.06589452524345336</v>
       </c>
       <c r="C83">
-        <v>3875.195613381556</v>
+        <v>3837.806631043375</v>
       </c>
       <c r="D83">
-        <v>8724.138613381556</v>
+        <v>8764.952631043376</v>
       </c>
       <c r="E83">
-        <v>6334.443</v>
+        <v>6412.646000000001</v>
       </c>
       <c r="F83">
-        <v>6334.443</v>
+        <v>6412.646000000001</v>
       </c>
       <c r="G83">
         <v>1485.5</v>
@@ -8099,28 +8099,28 @@
         <v>1017.3</v>
       </c>
       <c r="M83">
-        <v>366.1308054</v>
+        <v>370.6509388000001</v>
       </c>
       <c r="N83">
-        <v>651.1691946000001</v>
+        <v>646.6490612</v>
       </c>
       <c r="O83">
-        <v>162.79229865</v>
+        <v>161.6622653</v>
       </c>
       <c r="P83">
-        <v>488.3768959500001</v>
+        <v>484.9867959</v>
       </c>
       <c r="Q83">
-        <v>551.9768959500001</v>
+        <v>548.5867959</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.162500174655108</v>
+        <v>0.1685973624636298</v>
       </c>
       <c r="T83">
-        <v>2.339098620070637</v>
+        <v>2.461308579321976</v>
       </c>
       <c r="U83">
         <v>0.0578</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.778515178171348</v>
+        <v>2.744630846730233</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.06589452524345336</v>
+        <v>0.06580051730243622</v>
       </c>
       <c r="C84">
-        <v>3837.806631043375</v>
+        <v>3800.801322957915</v>
       </c>
       <c r="D84">
-        <v>8764.952631043376</v>
+        <v>8806.150322957916</v>
       </c>
       <c r="E84">
-        <v>6412.646000000001</v>
+        <v>6490.849000000001</v>
       </c>
       <c r="F84">
-        <v>6412.646000000001</v>
+        <v>6490.849000000001</v>
       </c>
       <c r="G84">
         <v>1485.5</v>
@@ -8181,28 +8181,28 @@
         <v>1017.3</v>
       </c>
       <c r="M84">
-        <v>370.6509388000001</v>
+        <v>375.1710722000001</v>
       </c>
       <c r="N84">
-        <v>646.6490612</v>
+        <v>642.1289277999999</v>
       </c>
       <c r="O84">
-        <v>161.6622653</v>
+        <v>160.53223195</v>
       </c>
       <c r="P84">
-        <v>484.9867959</v>
+        <v>481.5966958499999</v>
       </c>
       <c r="Q84">
-        <v>548.5867959</v>
+        <v>545.19669585</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1685973624636298</v>
+        <v>0.175411866484919</v>
       </c>
       <c r="T84">
-        <v>2.461308579321976</v>
+        <v>2.59789618083818</v>
       </c>
       <c r="U84">
         <v>0.0578</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.744630846730233</v>
+        <v>2.711563005203363</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.06580051730243622</v>
+        <v>0.06570650936141907</v>
       </c>
       <c r="C85">
-        <v>3800.801322957915</v>
+        <v>3764.185124798382</v>
       </c>
       <c r="D85">
-        <v>8806.150322957916</v>
+        <v>8847.737124798383</v>
       </c>
       <c r="E85">
-        <v>6490.849000000001</v>
+        <v>6569.052000000001</v>
       </c>
       <c r="F85">
-        <v>6490.849000000001</v>
+        <v>6569.052000000001</v>
       </c>
       <c r="G85">
         <v>1485.5</v>
@@ -8263,28 +8263,28 @@
         <v>1017.3</v>
       </c>
       <c r="M85">
-        <v>375.1710722000001</v>
+        <v>379.6912056</v>
       </c>
       <c r="N85">
-        <v>642.1289277999999</v>
+        <v>637.6087944000001</v>
       </c>
       <c r="O85">
-        <v>160.53223195</v>
+        <v>159.4021986</v>
       </c>
       <c r="P85">
-        <v>481.5966958499999</v>
+        <v>478.2065958000001</v>
       </c>
       <c r="Q85">
-        <v>545.19669585</v>
+        <v>541.8065958000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.175411866484919</v>
+        <v>0.1830781835088693</v>
       </c>
       <c r="T85">
-        <v>2.59789618083818</v>
+        <v>2.751557232543909</v>
       </c>
       <c r="U85">
         <v>0.0578</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.711563005203363</v>
+        <v>2.679282493236657</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.06570650936141906</v>
+        <v>0.06561250142040193</v>
       </c>
       <c r="C86">
-        <v>3764.185124798389</v>
+        <v>3727.963575404451</v>
       </c>
       <c r="D86">
-        <v>8847.737124798388</v>
+        <v>8889.718575404451</v>
       </c>
       <c r="E86">
-        <v>6569.052</v>
+        <v>6647.255</v>
       </c>
       <c r="F86">
-        <v>6569.052</v>
+        <v>6647.255</v>
       </c>
       <c r="G86">
         <v>1485.5</v>
@@ -8345,28 +8345,28 @@
         <v>1017.3</v>
       </c>
       <c r="M86">
-        <v>379.6912056</v>
+        <v>384.211339</v>
       </c>
       <c r="N86">
-        <v>637.6087944000001</v>
+        <v>633.088661</v>
       </c>
       <c r="O86">
-        <v>159.4021986</v>
+        <v>158.27216525</v>
       </c>
       <c r="P86">
-        <v>478.2065958000001</v>
+        <v>474.81649575</v>
       </c>
       <c r="Q86">
-        <v>541.8065958000001</v>
+        <v>538.41649575</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1830781835088691</v>
+        <v>0.1917666761360128</v>
       </c>
       <c r="T86">
-        <v>2.751557232543906</v>
+        <v>2.925706424477066</v>
       </c>
       <c r="U86">
         <v>0.0578</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.679282493236657</v>
+        <v>2.64776152272799</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.06561250142040193</v>
+        <v>0.06551849347938477</v>
       </c>
       <c r="C87">
-        <v>3727.963575404451</v>
+        <v>3692.1423192415</v>
       </c>
       <c r="D87">
-        <v>8889.718575404451</v>
+        <v>8932.100319241499</v>
       </c>
       <c r="E87">
-        <v>6647.255</v>
+        <v>6725.458</v>
       </c>
       <c r="F87">
-        <v>6647.255</v>
+        <v>6725.458</v>
       </c>
       <c r="G87">
         <v>1485.5</v>
@@ -8427,28 +8427,28 @@
         <v>1017.3</v>
       </c>
       <c r="M87">
-        <v>384.211339</v>
+        <v>388.7314724</v>
       </c>
       <c r="N87">
-        <v>633.088661</v>
+        <v>628.5685276</v>
       </c>
       <c r="O87">
-        <v>158.27216525</v>
+        <v>157.1421319</v>
       </c>
       <c r="P87">
-        <v>474.81649575</v>
+        <v>471.4263957000001</v>
       </c>
       <c r="Q87">
-        <v>538.41649575</v>
+        <v>535.0263957000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1917666761360128</v>
+        <v>0.2016963819956055</v>
       </c>
       <c r="T87">
-        <v>2.925706424477066</v>
+        <v>3.124734072400675</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.64776152272799</v>
+        <v>2.616973598045107</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.06551849347938477</v>
+        <v>0.06542448553836762</v>
       </c>
       <c r="C88">
-        <v>3692.1423192415</v>
+        <v>3656.727108930498</v>
       </c>
       <c r="D88">
-        <v>8932.100319241499</v>
+        <v>8974.888108930498</v>
       </c>
       <c r="E88">
-        <v>6725.458</v>
+        <v>6803.661</v>
       </c>
       <c r="F88">
-        <v>6725.458</v>
+        <v>6803.661</v>
       </c>
       <c r="G88">
         <v>1485.5</v>
@@ -8509,28 +8509,28 @@
         <v>1017.3</v>
       </c>
       <c r="M88">
-        <v>388.7314724</v>
+        <v>393.2516058</v>
       </c>
       <c r="N88">
-        <v>628.5685276</v>
+        <v>624.0483942000001</v>
       </c>
       <c r="O88">
-        <v>157.1421319</v>
+        <v>156.01209855</v>
       </c>
       <c r="P88">
-        <v>471.4263957000001</v>
+        <v>468.0362956500001</v>
       </c>
       <c r="Q88">
-        <v>535.0263957000001</v>
+        <v>531.6362956500001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2016963819956055</v>
+        <v>0.2131537349105201</v>
       </c>
       <c r="T88">
-        <v>3.124734072400675</v>
+        <v>3.354381358466379</v>
       </c>
       <c r="U88">
         <v>0.0578</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.616973598045107</v>
+        <v>2.586893441745738</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.06542448553836762</v>
+        <v>0.06533047759735047</v>
       </c>
       <c r="C89">
-        <v>3656.727108930498</v>
+        <v>3621.723807851034</v>
       </c>
       <c r="D89">
-        <v>8974.888108930498</v>
+        <v>9018.087807851034</v>
       </c>
       <c r="E89">
-        <v>6803.661</v>
+        <v>6881.864</v>
       </c>
       <c r="F89">
-        <v>6803.661</v>
+        <v>6881.864</v>
       </c>
       <c r="G89">
         <v>1485.5</v>
@@ -8591,28 +8591,28 @@
         <v>1017.3</v>
       </c>
       <c r="M89">
-        <v>393.2516058</v>
+        <v>397.7717392000001</v>
       </c>
       <c r="N89">
-        <v>624.0483942000001</v>
+        <v>619.5282608</v>
       </c>
       <c r="O89">
-        <v>156.01209855</v>
+        <v>154.8820652</v>
       </c>
       <c r="P89">
-        <v>468.0362956500001</v>
+        <v>464.6461956</v>
       </c>
       <c r="Q89">
-        <v>531.6362956500001</v>
+        <v>528.2461956</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2131537349105201</v>
+        <v>0.2265206466445873</v>
       </c>
       <c r="T89">
-        <v>3.354381358466379</v>
+        <v>3.622303192209701</v>
       </c>
       <c r="U89">
         <v>0.0578</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.586893441745738</v>
+        <v>2.557496925362263</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.06533047759735047</v>
+        <v>0.06523646965633331</v>
       </c>
       <c r="C90">
-        <v>3621.723807851034</v>
+        <v>3587.138392819806</v>
       </c>
       <c r="D90">
-        <v>9018.087807851034</v>
+        <v>9061.705392819806</v>
       </c>
       <c r="E90">
-        <v>6881.864</v>
+        <v>6960.067</v>
       </c>
       <c r="F90">
-        <v>6881.864</v>
+        <v>6960.067</v>
       </c>
       <c r="G90">
         <v>1485.5</v>
@@ -8673,28 +8673,28 @@
         <v>1017.3</v>
       </c>
       <c r="M90">
-        <v>397.7717392000001</v>
+        <v>402.2918726</v>
       </c>
       <c r="N90">
-        <v>619.5282608</v>
+        <v>615.0081274</v>
       </c>
       <c r="O90">
-        <v>154.8820652</v>
+        <v>153.75203185</v>
       </c>
       <c r="P90">
-        <v>464.6461956</v>
+        <v>461.2560955500001</v>
       </c>
       <c r="Q90">
-        <v>528.2461956</v>
+        <v>524.8560955500001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2265206466445873</v>
+        <v>0.2423179059666666</v>
       </c>
       <c r="T90">
-        <v>3.622303192209701</v>
+        <v>3.938938086633625</v>
       </c>
       <c r="U90">
         <v>0.0578</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.557496925362263</v>
+        <v>2.528761004852575</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.06523646965633331</v>
+        <v>0.06514246171531618</v>
       </c>
       <c r="C91">
-        <v>3587.138392819806</v>
+        <v>3552.976956847215</v>
       </c>
       <c r="D91">
-        <v>9061.705392819806</v>
+        <v>9105.746956847215</v>
       </c>
       <c r="E91">
-        <v>6960.067</v>
+        <v>7038.27</v>
       </c>
       <c r="F91">
-        <v>6960.067</v>
+        <v>7038.27</v>
       </c>
       <c r="G91">
         <v>1485.5</v>
@@ -8755,28 +8755,28 @@
         <v>1017.3</v>
       </c>
       <c r="M91">
-        <v>402.2918726</v>
+        <v>406.8120060000001</v>
       </c>
       <c r="N91">
-        <v>615.0081274</v>
+        <v>610.4879940000001</v>
       </c>
       <c r="O91">
-        <v>153.75203185</v>
+        <v>152.6219985</v>
       </c>
       <c r="P91">
-        <v>461.2560955500001</v>
+        <v>457.8659955000001</v>
       </c>
       <c r="Q91">
-        <v>524.8560955500001</v>
+        <v>521.4659955000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2423179059666666</v>
+        <v>0.2612746171531618</v>
       </c>
       <c r="T91">
-        <v>3.938938086633625</v>
+        <v>4.318899959942336</v>
       </c>
       <c r="U91">
         <v>0.0578</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.528761004852575</v>
+        <v>2.500663660354213</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.06514246171531618</v>
+        <v>0.06743720377429903</v>
       </c>
       <c r="C92">
-        <v>3552.976956847215</v>
+        <v>2509.060422959248</v>
       </c>
       <c r="D92">
-        <v>9105.746956847215</v>
+        <v>8140.033422959247</v>
       </c>
       <c r="E92">
-        <v>7038.27</v>
+        <v>7116.473</v>
       </c>
       <c r="F92">
-        <v>7038.27</v>
+        <v>7116.473</v>
       </c>
       <c r="G92">
         <v>1485.5</v>
@@ -8837,45 +8837,45 @@
         <v>1017.3</v>
       </c>
       <c r="M92">
-        <v>406.8120060000001</v>
+        <v>436.2397949</v>
       </c>
       <c r="N92">
-        <v>610.4879940000001</v>
+        <v>581.0602051000001</v>
       </c>
       <c r="O92">
-        <v>152.6219985</v>
+        <v>145.265051275</v>
       </c>
       <c r="P92">
-        <v>457.8659955000001</v>
+        <v>435.7951538250001</v>
       </c>
       <c r="Q92">
-        <v>521.4659955000001</v>
+        <v>499.3951538250001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2612746171531618</v>
+        <v>0.2844439308255448</v>
       </c>
       <c r="T92">
-        <v>4.318899959942336</v>
+        <v>4.783297805097426</v>
       </c>
       <c r="U92">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V92">
         <v>0.25</v>
       </c>
       <c r="W92">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y92">
-        <v>2.500663660354213</v>
+        <v>2.331974322134452</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.06743720377429903</v>
+        <v>0.06736944583328187</v>
       </c>
       <c r="C93">
-        <v>2509.060422959248</v>
+        <v>2456.428404653153</v>
       </c>
       <c r="D93">
-        <v>8140.033422959247</v>
+        <v>8165.604404653153</v>
       </c>
       <c r="E93">
-        <v>7116.473</v>
+        <v>7194.676</v>
       </c>
       <c r="F93">
-        <v>7116.473</v>
+        <v>7194.676</v>
       </c>
       <c r="G93">
         <v>1485.5</v>
@@ -8919,28 +8919,28 @@
         <v>1017.3</v>
       </c>
       <c r="M93">
-        <v>436.2397949</v>
+        <v>441.0336388</v>
       </c>
       <c r="N93">
-        <v>581.0602051000001</v>
+        <v>576.2663612000001</v>
       </c>
       <c r="O93">
-        <v>145.265051275</v>
+        <v>144.0665903</v>
       </c>
       <c r="P93">
-        <v>435.7951538250001</v>
+        <v>432.1997709000001</v>
       </c>
       <c r="Q93">
-        <v>499.3951538250001</v>
+        <v>495.7997709000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2844439308255448</v>
+        <v>0.3134055729160236</v>
       </c>
       <c r="T93">
-        <v>4.783297805097426</v>
+        <v>5.363795111541291</v>
       </c>
       <c r="U93">
         <v>0.0613</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.331974322134452</v>
+        <v>2.30662677515473</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.06736944583328187</v>
+        <v>0.06730168789226473</v>
       </c>
       <c r="C94">
-        <v>2456.428404653153</v>
+        <v>2403.957549236035</v>
       </c>
       <c r="D94">
-        <v>8165.604404653153</v>
+        <v>8191.336549236036</v>
       </c>
       <c r="E94">
-        <v>7194.676</v>
+        <v>7272.879000000001</v>
       </c>
       <c r="F94">
-        <v>7194.676</v>
+        <v>7272.879000000001</v>
       </c>
       <c r="G94">
         <v>1485.5</v>
@@ -9001,28 +9001,28 @@
         <v>1017.3</v>
       </c>
       <c r="M94">
-        <v>441.0336388</v>
+        <v>445.8274827000001</v>
       </c>
       <c r="N94">
-        <v>576.2663612000001</v>
+        <v>571.4725172999999</v>
       </c>
       <c r="O94">
-        <v>144.0665903</v>
+        <v>142.868129325</v>
       </c>
       <c r="P94">
-        <v>432.1997709000001</v>
+        <v>428.604387975</v>
       </c>
       <c r="Q94">
-        <v>495.7997709000001</v>
+        <v>492.204387975</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3134055729160236</v>
+        <v>0.3506419698894964</v>
       </c>
       <c r="T94">
-        <v>5.363795111541291</v>
+        <v>6.110148791254829</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.30662677515473</v>
+        <v>2.281824336712206</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.06730168789226473</v>
+        <v>0.06723392995124758</v>
       </c>
       <c r="C95">
-        <v>2403.957549236035</v>
+        <v>2351.649385134879</v>
       </c>
       <c r="D95">
-        <v>8191.336549236036</v>
+        <v>8217.231385134879</v>
       </c>
       <c r="E95">
-        <v>7272.879000000001</v>
+        <v>7351.082</v>
       </c>
       <c r="F95">
-        <v>7272.879000000001</v>
+        <v>7351.082</v>
       </c>
       <c r="G95">
         <v>1485.5</v>
@@ -9083,28 +9083,28 @@
         <v>1017.3</v>
       </c>
       <c r="M95">
-        <v>445.8274827000001</v>
+        <v>450.6213266</v>
       </c>
       <c r="N95">
-        <v>571.4725172999999</v>
+        <v>566.6786734</v>
       </c>
       <c r="O95">
-        <v>142.868129325</v>
+        <v>141.66966835</v>
       </c>
       <c r="P95">
-        <v>428.604387975</v>
+        <v>425.00900505</v>
       </c>
       <c r="Q95">
-        <v>492.204387975</v>
+        <v>488.60900505</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3506419698894964</v>
+        <v>0.40029049918746</v>
       </c>
       <c r="T95">
-        <v>6.110148791254829</v>
+        <v>7.10528703087288</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.281824336712206</v>
+        <v>2.257549609725906</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.06723392995124758</v>
+        <v>0.06916117201023043</v>
       </c>
       <c r="C96">
-        <v>2351.649385134879</v>
+        <v>1595.544012476063</v>
       </c>
       <c r="D96">
-        <v>8217.231385134879</v>
+        <v>7539.329012476063</v>
       </c>
       <c r="E96">
-        <v>7351.082</v>
+        <v>7429.285000000001</v>
       </c>
       <c r="F96">
-        <v>7351.082</v>
+        <v>7429.285000000001</v>
       </c>
       <c r="G96">
         <v>1485.5</v>
@@ -9165,45 +9165,45 @@
         <v>1017.3</v>
       </c>
       <c r="M96">
-        <v>450.6213266</v>
+        <v>476.2171685000001</v>
       </c>
       <c r="N96">
-        <v>566.6786734</v>
+        <v>541.0828315</v>
       </c>
       <c r="O96">
-        <v>141.66966835</v>
+        <v>135.270707875</v>
       </c>
       <c r="P96">
-        <v>425.00900505</v>
+        <v>405.812123625</v>
       </c>
       <c r="Q96">
-        <v>488.60900505</v>
+        <v>469.412123625</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.40029049918746</v>
+        <v>0.4697984402046092</v>
       </c>
       <c r="T96">
-        <v>7.10528703087288</v>
+        <v>8.498480566338156</v>
       </c>
       <c r="U96">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V96">
         <v>0.25</v>
       </c>
       <c r="W96">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y96">
-        <v>2.257549609725906</v>
+        <v>2.136210257190675</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.06916117201023043</v>
+        <v>0.06911441406921329</v>
       </c>
       <c r="C97">
-        <v>1595.544012476063</v>
+        <v>1532.461422546317</v>
       </c>
       <c r="D97">
-        <v>7539.329012476063</v>
+        <v>7554.449422546319</v>
       </c>
       <c r="E97">
-        <v>7429.285000000001</v>
+        <v>7507.488000000001</v>
       </c>
       <c r="F97">
-        <v>7429.285000000001</v>
+        <v>7507.488000000001</v>
       </c>
       <c r="G97">
         <v>1485.5</v>
@@ -9247,28 +9247,28 @@
         <v>1017.3</v>
       </c>
       <c r="M97">
-        <v>476.2171685000001</v>
+        <v>481.2299808000001</v>
       </c>
       <c r="N97">
-        <v>541.0828315</v>
+        <v>536.0700191999999</v>
       </c>
       <c r="O97">
-        <v>135.270707875</v>
+        <v>134.0175048</v>
       </c>
       <c r="P97">
-        <v>405.812123625</v>
+        <v>402.0525144</v>
       </c>
       <c r="Q97">
-        <v>469.412123625</v>
+        <v>465.6525144</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4697984402046092</v>
+        <v>0.574060351730333</v>
       </c>
       <c r="T97">
-        <v>8.498480566338156</v>
+        <v>10.58827086953607</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.136210257190675</v>
+        <v>2.113958067011605</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.06911441406921329</v>
+        <v>0.06906765612819614</v>
       </c>
       <c r="C98">
-        <v>1532.461422546318</v>
+        <v>1469.439603605996</v>
       </c>
       <c r="D98">
-        <v>7554.449422546319</v>
+        <v>7569.630603605996</v>
       </c>
       <c r="E98">
-        <v>7507.488</v>
+        <v>7585.691</v>
       </c>
       <c r="F98">
-        <v>7507.488</v>
+        <v>7585.691</v>
       </c>
       <c r="G98">
         <v>1485.5</v>
@@ -9329,28 +9329,28 @@
         <v>1017.3</v>
       </c>
       <c r="M98">
-        <v>481.2299808000001</v>
+        <v>486.2427931</v>
       </c>
       <c r="N98">
-        <v>536.0700191999999</v>
+        <v>531.0572069</v>
       </c>
       <c r="O98">
-        <v>134.0175048</v>
+        <v>132.764301725</v>
       </c>
       <c r="P98">
-        <v>402.0525144</v>
+        <v>398.292905175</v>
       </c>
       <c r="Q98">
-        <v>465.6525144</v>
+        <v>461.892905175</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5740603517303315</v>
+        <v>0.7478302042732038</v>
       </c>
       <c r="T98">
-        <v>10.58827086953604</v>
+        <v>14.07125470819921</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.113958067011605</v>
+        <v>2.092164684877465</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.06906765612819614</v>
+        <v>0.06902089818717899</v>
       </c>
       <c r="C99">
-        <v>1469.439603605996</v>
+        <v>1406.478922763159</v>
       </c>
       <c r="D99">
-        <v>7569.630603605996</v>
+        <v>7584.87292276316</v>
       </c>
       <c r="E99">
-        <v>7585.691</v>
+        <v>7663.894</v>
       </c>
       <c r="F99">
-        <v>7585.691</v>
+        <v>7663.894</v>
       </c>
       <c r="G99">
         <v>1485.5</v>
@@ -9411,28 +9411,28 @@
         <v>1017.3</v>
       </c>
       <c r="M99">
-        <v>486.2427931</v>
+        <v>491.2556054</v>
       </c>
       <c r="N99">
-        <v>531.0572069</v>
+        <v>526.0443946</v>
       </c>
       <c r="O99">
-        <v>132.764301725</v>
+        <v>131.51109865</v>
       </c>
       <c r="P99">
-        <v>398.292905175</v>
+        <v>394.53329595</v>
       </c>
       <c r="Q99">
-        <v>461.892905175</v>
+        <v>458.13329595</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7478302042732038</v>
+        <v>1.095369909358948</v>
       </c>
       <c r="T99">
-        <v>14.07125470819921</v>
+        <v>21.03722238552555</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.092164684877465</v>
+        <v>2.070816065644022</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.06902089818717899</v>
+        <v>0.06897414024616184</v>
       </c>
       <c r="C100">
-        <v>1406.478922763159</v>
+        <v>1343.5797500887</v>
       </c>
       <c r="D100">
-        <v>7584.87292276316</v>
+        <v>7600.176750088701</v>
       </c>
       <c r="E100">
-        <v>7663.894</v>
+        <v>7742.097</v>
       </c>
       <c r="F100">
-        <v>7663.894</v>
+        <v>7742.097</v>
       </c>
       <c r="G100">
         <v>1485.5</v>
@@ -9493,28 +9493,28 @@
         <v>1017.3</v>
       </c>
       <c r="M100">
-        <v>491.2556054</v>
+        <v>496.2684177</v>
       </c>
       <c r="N100">
-        <v>526.0443946</v>
+        <v>521.0315823000001</v>
       </c>
       <c r="O100">
-        <v>131.51109865</v>
+        <v>130.257895575</v>
       </c>
       <c r="P100">
-        <v>394.53329595</v>
+        <v>390.7736867250001</v>
       </c>
       <c r="Q100">
-        <v>458.13329595</v>
+        <v>454.3736867250001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.095369909358948</v>
+        <v>2.137989024616182</v>
       </c>
       <c r="T100">
-        <v>21.03722238552555</v>
+        <v>41.93512541750458</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.070816065644022</v>
+        <v>2.049898731647617</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.06897414024616184</v>
-      </c>
-      <c r="C101">
-        <v>1343.5797500887</v>
-      </c>
-      <c r="D101">
-        <v>7600.176750088701</v>
-      </c>
-      <c r="E101">
-        <v>7742.097</v>
-      </c>
-      <c r="F101">
-        <v>7742.097</v>
-      </c>
-      <c r="G101">
-        <v>1485.5</v>
-      </c>
-      <c r="H101">
-        <v>7820.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1080.9</v>
-      </c>
-      <c r="K101">
-        <v>63.6</v>
-      </c>
-      <c r="L101">
-        <v>1017.3</v>
-      </c>
-      <c r="M101">
-        <v>496.2684177</v>
-      </c>
-      <c r="N101">
-        <v>521.0315823000001</v>
-      </c>
-      <c r="O101">
-        <v>130.257895575</v>
-      </c>
-      <c r="P101">
-        <v>390.7736867250001</v>
-      </c>
-      <c r="Q101">
-        <v>454.3736867250001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.137989024616182</v>
-      </c>
-      <c r="T101">
-        <v>41.93512541750458</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.04807500000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.049898731647617</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
